--- a/AAII_Financials/Quarterly/KEWL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KEWL_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/KEWL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KEWL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="92">
   <si>
     <t>KEWL</t>
   </si>
@@ -656,158 +656,165 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44469</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44377</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44286</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44196</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44104</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44012</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43921</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43830</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43738</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43646</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43555</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43465</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43373</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E8" s="3">
         <v>100</v>
       </c>
       <c r="F8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G8" s="3">
         <v>200</v>
       </c>
       <c r="H8" s="3">
+        <v>200</v>
+      </c>
+      <c r="I8" s="3">
         <v>6400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>6200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -818,114 +825,120 @@
         <v>100</v>
       </c>
       <c r="F9" s="3">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H9" s="3">
+        <v>100</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3">
         <v>3900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>8100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E10" s="3">
         <v>0</v>
       </c>
       <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
         <v>200</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="3">
         <v>2500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-3400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -947,8 +960,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1006,8 +1020,11 @@
       <c r="U12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1065,8 +1082,11 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1091,8 +1111,8 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1104,28 +1124,31 @@
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>200</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>200</v>
-      </c>
-      <c r="S14" s="3">
-        <v>300</v>
       </c>
       <c r="T14" s="3">
         <v>300</v>
       </c>
       <c r="U14" s="3">
+        <v>300</v>
+      </c>
+      <c r="V14" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1183,8 +1206,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,8 +1229,9 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1218,111 +1245,117 @@
         <v>400</v>
       </c>
       <c r="G17" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="H17" s="3">
+        <v>100</v>
+      </c>
+      <c r="I17" s="3">
         <v>4400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4600</v>
       </c>
-      <c r="K17" s="3">
-        <v>100</v>
-      </c>
       <c r="L17" s="3">
+        <v>100</v>
+      </c>
+      <c r="M17" s="3">
         <v>4100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="E18" s="3">
         <v>-300</v>
       </c>
       <c r="F18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G18" s="3">
         <v>-200</v>
       </c>
-      <c r="G18" s="3">
-        <v>100</v>
-      </c>
       <c r="H18" s="3">
+        <v>100</v>
+      </c>
+      <c r="I18" s="3">
         <v>2000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3100</v>
       </c>
-      <c r="K18" s="3">
-        <v>100</v>
-      </c>
       <c r="L18" s="3">
+        <v>100</v>
+      </c>
+      <c r="M18" s="3">
         <v>1300</v>
       </c>
-      <c r="M18" s="3">
-        <v>0</v>
-      </c>
       <c r="N18" s="3">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3">
         <v>900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>600</v>
       </c>
-      <c r="S18" s="3">
-        <v>100</v>
-      </c>
       <c r="T18" s="3">
+        <v>100</v>
+      </c>
+      <c r="U18" s="3">
         <v>1400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,17 +1377,18 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>200</v>
+      </c>
+      <c r="E20" s="3">
         <v>500</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
@@ -1371,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1392,78 +1426,84 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>1500</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
       <c r="U20" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
         <v>200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1500</v>
       </c>
-      <c r="M21" s="3">
-        <v>100</v>
-      </c>
       <c r="N21" s="3">
+        <v>100</v>
+      </c>
+      <c r="O21" s="3">
         <v>1100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1479,17 +1519,17 @@
       <c r="G22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L22" s="3">
         <v>100</v>
@@ -1507,7 +1547,7 @@
         <v>100</v>
       </c>
       <c r="Q22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R22" s="3">
         <v>200</v>
@@ -1521,67 +1561,73 @@
       <c r="U22" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3">
         <v>200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-200</v>
       </c>
-      <c r="G23" s="3">
-        <v>100</v>
-      </c>
       <c r="H23" s="3">
+        <v>100</v>
+      </c>
+      <c r="I23" s="3">
         <v>2000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3100</v>
       </c>
-      <c r="K23" s="3">
-        <v>100</v>
-      </c>
       <c r="L23" s="3">
+        <v>100</v>
+      </c>
+      <c r="M23" s="3">
         <v>1200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>800</v>
-      </c>
-      <c r="O23" s="3">
-        <v>600</v>
       </c>
       <c r="P23" s="3">
         <v>600</v>
       </c>
       <c r="Q23" s="3">
+        <v>600</v>
+      </c>
+      <c r="R23" s="3">
         <v>-300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1589,58 +1635,61 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>500</v>
       </c>
-      <c r="I24" s="3">
-        <v>100</v>
-      </c>
       <c r="J24" s="3">
+        <v>100</v>
+      </c>
+      <c r="K24" s="3">
         <v>800</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
-        <v>100</v>
-      </c>
       <c r="P24" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-200</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,126 +1747,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E26" s="3">
-        <v>-200</v>
+        <v>100</v>
       </c>
       <c r="F26" s="3">
         <v>-200</v>
       </c>
       <c r="G26" s="3">
-        <v>100</v>
+        <v>-200</v>
       </c>
       <c r="H26" s="3">
+        <v>100</v>
+      </c>
+      <c r="I26" s="3">
         <v>1500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2300</v>
       </c>
-      <c r="K26" s="3">
-        <v>100</v>
-      </c>
       <c r="L26" s="3">
+        <v>100</v>
+      </c>
+      <c r="M26" s="3">
         <v>900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1500</v>
       </c>
-      <c r="S26" s="3">
-        <v>100</v>
-      </c>
       <c r="T26" s="3">
+        <v>100</v>
+      </c>
+      <c r="U26" s="3">
         <v>1200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E27" s="3">
-        <v>-200</v>
+        <v>100</v>
       </c>
       <c r="F27" s="3">
         <v>-200</v>
       </c>
       <c r="G27" s="3">
-        <v>100</v>
+        <v>-200</v>
       </c>
       <c r="H27" s="3">
+        <v>100</v>
+      </c>
+      <c r="I27" s="3">
         <v>1500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2300</v>
       </c>
-      <c r="K27" s="3">
-        <v>100</v>
-      </c>
       <c r="L27" s="3">
+        <v>100</v>
+      </c>
+      <c r="M27" s="3">
         <v>900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1500</v>
       </c>
-      <c r="S27" s="3">
-        <v>100</v>
-      </c>
       <c r="T27" s="3">
+        <v>100</v>
+      </c>
+      <c r="U27" s="3">
         <v>1200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,8 +1933,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1884,34 +1945,34 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>-200</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-300</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>113100</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K29" s="3">
+      <c r="K29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L29" s="3">
         <v>3300</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
@@ -1934,8 +1995,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2057,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,17 +2119,20 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-500</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
@@ -2079,11 +2149,11 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -2100,78 +2170,84 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-1500</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E33" s="3">
-        <v>-400</v>
+        <v>100</v>
       </c>
       <c r="F33" s="3">
         <v>-400</v>
       </c>
       <c r="G33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H33" s="3">
         <v>113200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1500</v>
       </c>
-      <c r="S33" s="3">
-        <v>100</v>
-      </c>
       <c r="T33" s="3">
+        <v>100</v>
+      </c>
+      <c r="U33" s="3">
         <v>1200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2305,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E35" s="3">
-        <v>-400</v>
+        <v>100</v>
       </c>
       <c r="F35" s="3">
         <v>-400</v>
       </c>
       <c r="G35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H35" s="3">
         <v>113200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1500</v>
       </c>
-      <c r="S35" s="3">
-        <v>100</v>
-      </c>
       <c r="T35" s="3">
+        <v>100</v>
+      </c>
+      <c r="U35" s="3">
         <v>1200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44469</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44377</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44286</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44196</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44104</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44012</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43921</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43830</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43738</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43646</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43555</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43465</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43373</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2460,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,67 +2484,71 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E41" s="3">
         <v>10100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>41900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5600</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2516,67 +2606,73 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F43" s="3">
-        <v>100</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H43" s="3">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3">
+        <v>100</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I43" s="3">
         <v>1200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2000</v>
-      </c>
-      <c r="L43" s="3">
-        <v>1000</v>
       </c>
       <c r="M43" s="3">
         <v>1000</v>
       </c>
       <c r="N43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O43" s="3">
         <v>1300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>900</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2592,30 +2688,30 @@
       <c r="G44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H44" s="3">
-        <v>200</v>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I44" s="3">
         <v>200</v>
       </c>
       <c r="J44" s="3">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="K44" s="3">
         <v>600</v>
       </c>
       <c r="L44" s="3">
+        <v>600</v>
+      </c>
+      <c r="M44" s="3">
         <v>300</v>
       </c>
-      <c r="M44" s="3">
-        <v>100</v>
-      </c>
       <c r="N44" s="3">
+        <v>100</v>
+      </c>
+      <c r="O44" s="3">
         <v>200</v>
       </c>
-      <c r="O44" s="3">
-        <v>100</v>
-      </c>
       <c r="P44" s="3">
         <v>100</v>
       </c>
@@ -2625,8 +2721,8 @@
       <c r="R44" s="3">
         <v>100</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>8</v>
+      <c r="S44" s="3">
+        <v>100</v>
       </c>
       <c r="T44" s="3" t="s">
         <v>8</v>
@@ -2634,8 +2730,11 @@
       <c r="U44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2646,25 +2745,25 @@
         <v>0</v>
       </c>
       <c r="F45" s="3">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3">
         <v>9300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>11100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>300</v>
-      </c>
-      <c r="L45" s="3">
-        <v>600</v>
       </c>
       <c r="M45" s="3">
         <v>600</v>
@@ -2673,7 +2772,7 @@
         <v>600</v>
       </c>
       <c r="O45" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="P45" s="3">
         <v>400</v>
@@ -2684,8 +2783,8 @@
       <c r="R45" s="3">
         <v>400</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>8</v>
+      <c r="S45" s="3">
+        <v>400</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>8</v>
@@ -2693,67 +2792,73 @@
       <c r="U45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E46" s="3">
         <v>10200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>10000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>13000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>53000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>7000</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2811,58 +2916,61 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5600</v>
+        <v>7100</v>
       </c>
       <c r="E48" s="3">
         <v>5600</v>
       </c>
       <c r="F48" s="3">
-        <v>5500</v>
+        <v>5600</v>
       </c>
       <c r="G48" s="3">
         <v>5500</v>
       </c>
       <c r="H48" s="3">
+        <v>5500</v>
+      </c>
+      <c r="I48" s="3">
         <v>32100</v>
-      </c>
-      <c r="I48" s="3">
-        <v>27200</v>
       </c>
       <c r="J48" s="3">
         <v>27200</v>
       </c>
       <c r="K48" s="3">
-        <v>27700</v>
+        <v>27200</v>
       </c>
       <c r="L48" s="3">
         <v>27700</v>
       </c>
       <c r="M48" s="3">
+        <v>27700</v>
+      </c>
+      <c r="N48" s="3">
         <v>27900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>28000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>28200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>28300</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>32800</v>
       </c>
       <c r="R48" s="3">
         <v>32800</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>8</v>
+      <c r="S48" s="3">
+        <v>32800</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>8</v>
@@ -2870,8 +2978,11 @@
       <c r="U48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2929,8 +3040,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3102,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,8 +3164,11 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3061,23 +3181,23 @@
       <c r="F52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
+      <c r="G52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I52" s="3">
         <v>100</v>
       </c>
       <c r="J52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K52" s="3">
         <v>200</v>
       </c>
       <c r="L52" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="M52" s="3">
         <v>400</v>
@@ -3097,8 +3217,8 @@
       <c r="R52" s="3">
         <v>400</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>8</v>
+      <c r="S52" s="3">
+        <v>400</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>8</v>
@@ -3106,8 +3226,11 @@
       <c r="U52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,8 +3288,11 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -3174,58 +3300,61 @@
         <v>15700</v>
       </c>
       <c r="E54" s="3">
+        <v>15700</v>
+      </c>
+      <c r="F54" s="3">
         <v>15600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>18500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>58500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>35000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>33400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>34300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>32100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>33000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>31700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>32200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>32700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>36200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>35300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>40200</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3376,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,8 +3400,9 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3284,53 +3415,56 @@
       <c r="F57" s="3">
         <v>0</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="G57" s="3">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>300</v>
       </c>
-      <c r="J57" s="3">
-        <v>100</v>
-      </c>
       <c r="K57" s="3">
+        <v>100</v>
+      </c>
+      <c r="L57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>200</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3346,20 +3480,20 @@
       <c r="G58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H58" s="3">
-        <v>1500</v>
+      <c r="H58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I58" s="3">
         <v>1500</v>
       </c>
       <c r="J58" s="3">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="K58" s="3">
         <v>2500</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>8</v>
+      <c r="L58" s="3">
+        <v>2500</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>8</v>
@@ -3367,14 +3501,14 @@
       <c r="N58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -3388,8 +3522,11 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3397,63 +3534,66 @@
         <v>0</v>
       </c>
       <c r="E59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3">
         <v>39500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>700</v>
-      </c>
-      <c r="M59" s="3">
-        <v>500</v>
       </c>
       <c r="N59" s="3">
         <v>500</v>
       </c>
       <c r="O59" s="3">
+        <v>500</v>
+      </c>
+      <c r="P59" s="3">
         <v>700</v>
-      </c>
-      <c r="P59" s="3">
-        <v>500</v>
       </c>
       <c r="Q59" s="3">
         <v>500</v>
       </c>
       <c r="R59" s="3">
+        <v>500</v>
+      </c>
+      <c r="S59" s="3">
         <v>1100</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E60" s="3">
         <v>100</v>
@@ -3462,52 +3602,55 @@
         <v>100</v>
       </c>
       <c r="G60" s="3">
+        <v>100</v>
+      </c>
+      <c r="H60" s="3">
         <v>39500</v>
-      </c>
-      <c r="H60" s="3">
-        <v>2300</v>
       </c>
       <c r="I60" s="3">
         <v>2300</v>
       </c>
       <c r="J60" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K60" s="3">
         <v>3600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>700</v>
-      </c>
-      <c r="O60" s="3">
-        <v>900</v>
       </c>
       <c r="P60" s="3">
         <v>900</v>
       </c>
       <c r="Q60" s="3">
+        <v>900</v>
+      </c>
+      <c r="R60" s="3">
         <v>700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1300</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3524,7 +3667,7 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
         <v>3500</v>
@@ -3533,40 +3676,43 @@
         <v>3500</v>
       </c>
       <c r="K61" s="3">
+        <v>3500</v>
+      </c>
+      <c r="L61" s="3">
         <v>4000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9600</v>
-      </c>
-      <c r="M61" s="3">
-        <v>9500</v>
       </c>
       <c r="N61" s="3">
         <v>9500</v>
       </c>
       <c r="O61" s="3">
+        <v>9500</v>
+      </c>
+      <c r="P61" s="3">
         <v>10000</v>
-      </c>
-      <c r="P61" s="3">
-        <v>14000</v>
       </c>
       <c r="Q61" s="3">
         <v>14000</v>
       </c>
       <c r="R61" s="3">
+        <v>14000</v>
+      </c>
+      <c r="S61" s="3">
         <v>18000</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3574,29 +3720,29 @@
         <v>300</v>
       </c>
       <c r="E62" s="3">
+        <v>300</v>
+      </c>
+      <c r="F62" s="3">
         <v>200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>900</v>
-      </c>
-      <c r="I62" s="3">
-        <v>700</v>
       </c>
       <c r="J62" s="3">
         <v>700</v>
       </c>
       <c r="K62" s="3">
+        <v>700</v>
+      </c>
+      <c r="L62" s="3">
         <v>200</v>
       </c>
-      <c r="L62" s="3">
-        <v>100</v>
-      </c>
       <c r="M62" s="3">
         <v>100</v>
       </c>
@@ -3613,19 +3759,22 @@
         <v>100</v>
       </c>
       <c r="R62" s="3">
+        <v>100</v>
+      </c>
+      <c r="S62" s="3">
         <v>200</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3832,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3894,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,8 +3956,11 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -3813,55 +3971,58 @@
         <v>300</v>
       </c>
       <c r="F66" s="3">
+        <v>300</v>
+      </c>
+      <c r="G66" s="3">
         <v>500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>40100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>15000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>14900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>19500</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4044,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4104,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4166,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4060,8 +4228,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,8 +4290,11 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -4128,58 +4302,61 @@
         <v>15300</v>
       </c>
       <c r="E72" s="3">
+        <v>15300</v>
+      </c>
+      <c r="F72" s="3">
         <v>15200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>17900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>18300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>28300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>26900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>26500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>24200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>22200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>21100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>21700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>21500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>21100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>20400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>20600</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4414,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4476,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,8 +4538,11 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -4364,58 +4550,61 @@
         <v>15400</v>
       </c>
       <c r="E76" s="3">
+        <v>15400</v>
+      </c>
+      <c r="F76" s="3">
         <v>15200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>18000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>18400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>28400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>26900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>26500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>24300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>22200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>21200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>21800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>21600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>21200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>20500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>20700</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4662,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44469</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44377</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44286</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44196</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44104</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44012</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43921</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43830</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43738</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43646</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43555</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43465</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43373</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E81" s="3">
-        <v>-400</v>
+        <v>100</v>
       </c>
       <c r="F81" s="3">
         <v>-400</v>
       </c>
       <c r="G81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H81" s="3">
         <v>113200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1500</v>
       </c>
-      <c r="S81" s="3">
-        <v>100</v>
-      </c>
       <c r="T81" s="3">
+        <v>100</v>
+      </c>
+      <c r="U81" s="3">
         <v>1200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,8 +4817,9 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4633,29 +4832,29 @@
       <c r="F83" s="3">
         <v>0</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I83" s="3">
         <v>200</v>
       </c>
-      <c r="I83" s="3">
-        <v>100</v>
-      </c>
       <c r="J83" s="3">
+        <v>100</v>
+      </c>
+      <c r="K83" s="3">
         <v>200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>200</v>
       </c>
-      <c r="M83" s="3">
-        <v>100</v>
-      </c>
       <c r="N83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O83" s="3">
         <v>200</v>
@@ -4664,10 +4863,10 @@
         <v>200</v>
       </c>
       <c r="Q83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S83" s="3">
         <v>200</v>
@@ -4676,10 +4875,13 @@
         <v>200</v>
       </c>
       <c r="U83" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="V83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4939,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5001,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5063,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5125,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,67 +5187,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="E89" s="3">
+        <v>100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-39300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1100</v>
       </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
       <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3">
         <v>1400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>300</v>
       </c>
-      <c r="N89" s="3">
-        <v>100</v>
-      </c>
       <c r="O89" s="3">
+        <v>100</v>
+      </c>
+      <c r="P89" s="3">
         <v>1200</v>
       </c>
-      <c r="P89" s="3">
-        <v>100</v>
-      </c>
       <c r="Q89" s="3">
+        <v>100</v>
+      </c>
+      <c r="R89" s="3">
         <v>-700</v>
       </c>
-      <c r="R89" s="3">
-        <v>100</v>
-      </c>
       <c r="S89" s="3">
+        <v>100</v>
+      </c>
+      <c r="T89" s="3">
         <v>-100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,35 +5275,36 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-1500</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-5200</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
@@ -5106,16 +5327,19 @@
         <v>0</v>
       </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5397,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,67 +5459,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-1500</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>172600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>2700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1600</v>
-      </c>
-      <c r="L94" s="3">
-        <v>200</v>
       </c>
       <c r="M94" s="3">
         <v>200</v>
       </c>
       <c r="N94" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O94" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P94" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q94" s="3">
         <v>4400</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>3200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>1200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,8 +5547,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5329,11 +5563,11 @@
         <v>0</v>
       </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>-119200</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
@@ -5373,8 +5607,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5669,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5731,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,67 +5793,73 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-2300</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-125700</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-1000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4600</v>
       </c>
-      <c r="L100" s="3">
-        <v>100</v>
-      </c>
       <c r="M100" s="3">
+        <v>100</v>
+      </c>
+      <c r="N100" s="3">
         <v>-500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-400</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5668,63 +5917,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>100</v>
+        <v>-1600</v>
       </c>
       <c r="E102" s="3">
+        <v>100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-2900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-39300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>50700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1400</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>-700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>4700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KEWL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KEWL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
   <si>
     <t>KEWL</t>
   </si>
@@ -656,170 +656,177 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44561</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44469</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44377</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44286</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44196</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44104</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44012</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43921</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43830</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43738</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43646</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43555</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43465</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43373</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>100</v>
+      </c>
+      <c r="E8" s="3">
         <v>200</v>
       </c>
-      <c r="E8" s="3">
-        <v>100</v>
-      </c>
       <c r="F8" s="3">
         <v>100</v>
       </c>
       <c r="G8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H8" s="3">
         <v>200</v>
       </c>
       <c r="I8" s="3">
+        <v>200</v>
+      </c>
+      <c r="J8" s="3">
         <v>6400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>9500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>6200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E9" s="3">
         <v>100</v>
@@ -828,55 +835,58 @@
         <v>100</v>
       </c>
       <c r="G9" s="3">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I9" s="3">
+        <v>100</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3">
         <v>3900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>8100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -884,61 +894,64 @@
         <v>100</v>
       </c>
       <c r="E10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F10" s="3">
         <v>0</v>
       </c>
       <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
         <v>200</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="I10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="3">
         <v>2500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-3400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -961,8 +974,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1023,8 +1037,11 @@
       <c r="V12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1085,37 +1102,40 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1127,28 +1147,31 @@
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>200</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>200</v>
-      </c>
-      <c r="T14" s="3">
-        <v>300</v>
       </c>
       <c r="U14" s="3">
         <v>300</v>
       </c>
       <c r="V14" s="3">
+        <v>300</v>
+      </c>
+      <c r="W14" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1209,8 +1232,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,13 +1256,14 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E17" s="3">
         <v>400</v>
@@ -1248,52 +1275,55 @@
         <v>400</v>
       </c>
       <c r="H17" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="I17" s="3">
+        <v>100</v>
+      </c>
+      <c r="J17" s="3">
         <v>4400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4600</v>
       </c>
-      <c r="L17" s="3">
-        <v>100</v>
-      </c>
       <c r="M17" s="3">
+        <v>100</v>
+      </c>
+      <c r="N17" s="3">
         <v>4100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1301,61 +1331,64 @@
         <v>-200</v>
       </c>
       <c r="E18" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="F18" s="3">
         <v>-300</v>
       </c>
       <c r="G18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H18" s="3">
         <v>-200</v>
       </c>
-      <c r="H18" s="3">
-        <v>100</v>
-      </c>
       <c r="I18" s="3">
+        <v>100</v>
+      </c>
+      <c r="J18" s="3">
         <v>2000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3100</v>
       </c>
-      <c r="L18" s="3">
-        <v>100</v>
-      </c>
       <c r="M18" s="3">
+        <v>100</v>
+      </c>
+      <c r="N18" s="3">
         <v>1300</v>
       </c>
-      <c r="N18" s="3">
-        <v>0</v>
-      </c>
       <c r="O18" s="3">
+        <v>0</v>
+      </c>
+      <c r="P18" s="3">
         <v>900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>600</v>
       </c>
-      <c r="T18" s="3">
-        <v>100</v>
-      </c>
       <c r="U18" s="3">
+        <v>100</v>
+      </c>
+      <c r="V18" s="3">
         <v>1400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,8 +1411,9 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1387,11 +1421,11 @@
         <v>200</v>
       </c>
       <c r="E20" s="3">
+        <v>200</v>
+      </c>
+      <c r="F20" s="3">
         <v>500</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
@@ -1408,10 +1442,10 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1429,19 +1463,22 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>1500</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
       <c r="V20" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1449,61 +1486,64 @@
         <v>0</v>
       </c>
       <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1500</v>
       </c>
-      <c r="N21" s="3">
-        <v>100</v>
-      </c>
       <c r="O21" s="3">
+        <v>100</v>
+      </c>
+      <c r="P21" s="3">
         <v>1100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1522,17 +1562,17 @@
       <c r="H22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M22" s="3">
         <v>100</v>
@@ -1550,7 +1590,7 @@
         <v>100</v>
       </c>
       <c r="R22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S22" s="3">
         <v>200</v>
@@ -1564,8 +1604,11 @@
       <c r="V22" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1573,61 +1616,64 @@
         <v>0</v>
       </c>
       <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
         <v>200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-200</v>
       </c>
-      <c r="H23" s="3">
-        <v>100</v>
-      </c>
       <c r="I23" s="3">
+        <v>100</v>
+      </c>
+      <c r="J23" s="3">
         <v>2000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3100</v>
       </c>
-      <c r="L23" s="3">
-        <v>100</v>
-      </c>
       <c r="M23" s="3">
+        <v>100</v>
+      </c>
+      <c r="N23" s="3">
         <v>1200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>800</v>
-      </c>
-      <c r="P23" s="3">
-        <v>600</v>
       </c>
       <c r="Q23" s="3">
         <v>600</v>
       </c>
       <c r="R23" s="3">
+        <v>600</v>
+      </c>
+      <c r="S23" s="3">
         <v>-300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1638,58 +1684,61 @@
         <v>0</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>500</v>
       </c>
-      <c r="J24" s="3">
-        <v>100</v>
-      </c>
       <c r="K24" s="3">
+        <v>100</v>
+      </c>
+      <c r="L24" s="3">
         <v>800</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
-        <v>100</v>
-      </c>
       <c r="Q24" s="3">
+        <v>100</v>
+      </c>
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-200</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,8 +1799,11 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1759,61 +1811,64 @@
         <v>0</v>
       </c>
       <c r="E26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F26" s="3">
-        <v>-200</v>
+        <v>100</v>
       </c>
       <c r="G26" s="3">
         <v>-200</v>
       </c>
       <c r="H26" s="3">
-        <v>100</v>
+        <v>-200</v>
       </c>
       <c r="I26" s="3">
+        <v>100</v>
+      </c>
+      <c r="J26" s="3">
         <v>1500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2300</v>
       </c>
-      <c r="L26" s="3">
-        <v>100</v>
-      </c>
       <c r="M26" s="3">
+        <v>100</v>
+      </c>
+      <c r="N26" s="3">
         <v>900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1500</v>
       </c>
-      <c r="T26" s="3">
-        <v>100</v>
-      </c>
       <c r="U26" s="3">
+        <v>100</v>
+      </c>
+      <c r="V26" s="3">
         <v>1200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1821,61 +1876,64 @@
         <v>0</v>
       </c>
       <c r="E27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F27" s="3">
-        <v>-200</v>
+        <v>100</v>
       </c>
       <c r="G27" s="3">
         <v>-200</v>
       </c>
       <c r="H27" s="3">
-        <v>100</v>
+        <v>-200</v>
       </c>
       <c r="I27" s="3">
+        <v>100</v>
+      </c>
+      <c r="J27" s="3">
         <v>1500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2300</v>
       </c>
-      <c r="L27" s="3">
-        <v>100</v>
-      </c>
       <c r="M27" s="3">
+        <v>100</v>
+      </c>
+      <c r="N27" s="3">
         <v>900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1500</v>
       </c>
-      <c r="T27" s="3">
-        <v>100</v>
-      </c>
       <c r="U27" s="3">
+        <v>100</v>
+      </c>
+      <c r="V27" s="3">
         <v>1200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,46 +1994,49 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>-200</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-300</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>113100</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L29" s="3">
+      <c r="L29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M29" s="3">
         <v>3300</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -1998,8 +2059,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2124,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,8 +2189,11 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2131,11 +2201,11 @@
         <v>-200</v>
       </c>
       <c r="E32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-500</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
@@ -2152,11 +2222,11 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -2173,19 +2243,22 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-1500</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2193,61 +2266,64 @@
         <v>0</v>
       </c>
       <c r="E33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F33" s="3">
-        <v>-400</v>
+        <v>100</v>
       </c>
       <c r="G33" s="3">
         <v>-400</v>
       </c>
       <c r="H33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I33" s="3">
         <v>113200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1500</v>
       </c>
-      <c r="T33" s="3">
-        <v>100</v>
-      </c>
       <c r="U33" s="3">
+        <v>100</v>
+      </c>
+      <c r="V33" s="3">
         <v>1200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,8 +2384,11 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2317,128 +2396,134 @@
         <v>0</v>
       </c>
       <c r="E35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F35" s="3">
-        <v>-400</v>
+        <v>100</v>
       </c>
       <c r="G35" s="3">
         <v>-400</v>
       </c>
       <c r="H35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I35" s="3">
         <v>113200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1500</v>
       </c>
-      <c r="T35" s="3">
-        <v>100</v>
-      </c>
       <c r="U35" s="3">
+        <v>100</v>
+      </c>
+      <c r="V35" s="3">
         <v>1200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44561</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44469</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44377</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44286</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44196</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44104</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44012</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43921</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43830</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43738</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43646</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43555</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43465</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43373</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2546,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,70 +2571,74 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E41" s="3">
         <v>8400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>41900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5600</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2609,8 +2699,11 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2618,61 +2711,64 @@
         <v>200</v>
       </c>
       <c r="E43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G43" s="3">
-        <v>100</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I43" s="3">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3">
+        <v>100</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J43" s="3">
         <v>1200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2000</v>
-      </c>
-      <c r="M43" s="3">
-        <v>1000</v>
       </c>
       <c r="N43" s="3">
         <v>1000</v>
       </c>
       <c r="O43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P43" s="3">
         <v>1300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>900</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2691,30 +2787,30 @@
       <c r="H44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I44" s="3">
-        <v>200</v>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J44" s="3">
         <v>200</v>
       </c>
       <c r="K44" s="3">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="L44" s="3">
         <v>600</v>
       </c>
       <c r="M44" s="3">
+        <v>600</v>
+      </c>
+      <c r="N44" s="3">
         <v>300</v>
       </c>
-      <c r="N44" s="3">
-        <v>100</v>
-      </c>
       <c r="O44" s="3">
+        <v>100</v>
+      </c>
+      <c r="P44" s="3">
         <v>200</v>
       </c>
-      <c r="P44" s="3">
-        <v>100</v>
-      </c>
       <c r="Q44" s="3">
         <v>100</v>
       </c>
@@ -2724,8 +2820,8 @@
       <c r="S44" s="3">
         <v>100</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>8</v>
+      <c r="T44" s="3">
+        <v>100</v>
       </c>
       <c r="U44" s="3" t="s">
         <v>8</v>
@@ -2733,8 +2829,11 @@
       <c r="V44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2748,25 +2847,25 @@
         <v>0</v>
       </c>
       <c r="G45" s="3">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3">
         <v>9300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>300</v>
-      </c>
-      <c r="M45" s="3">
-        <v>600</v>
       </c>
       <c r="N45" s="3">
         <v>600</v>
@@ -2775,7 +2874,7 @@
         <v>600</v>
       </c>
       <c r="P45" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="Q45" s="3">
         <v>400</v>
@@ -2786,8 +2885,8 @@
       <c r="S45" s="3">
         <v>400</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>8</v>
+      <c r="T45" s="3">
+        <v>400</v>
       </c>
       <c r="U45" s="3" t="s">
         <v>8</v>
@@ -2795,93 +2894,99 @@
       <c r="V45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E46" s="3">
         <v>8600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>10200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>53000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>7600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>7000</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>2000</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2919,61 +3024,64 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E48" s="3">
         <v>7100</v>
-      </c>
-      <c r="E48" s="3">
-        <v>5600</v>
       </c>
       <c r="F48" s="3">
         <v>5600</v>
       </c>
       <c r="G48" s="3">
-        <v>5500</v>
+        <v>5600</v>
       </c>
       <c r="H48" s="3">
         <v>5500</v>
       </c>
       <c r="I48" s="3">
+        <v>5500</v>
+      </c>
+      <c r="J48" s="3">
         <v>32100</v>
-      </c>
-      <c r="J48" s="3">
-        <v>27200</v>
       </c>
       <c r="K48" s="3">
         <v>27200</v>
       </c>
       <c r="L48" s="3">
-        <v>27700</v>
+        <v>27200</v>
       </c>
       <c r="M48" s="3">
         <v>27700</v>
       </c>
       <c r="N48" s="3">
+        <v>27700</v>
+      </c>
+      <c r="O48" s="3">
         <v>27900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>28000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>28200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>28300</v>
-      </c>
-      <c r="R48" s="3">
-        <v>32800</v>
       </c>
       <c r="S48" s="3">
         <v>32800</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>8</v>
+      <c r="T48" s="3">
+        <v>32800</v>
       </c>
       <c r="U48" s="3" t="s">
         <v>8</v>
@@ -2981,8 +3089,11 @@
       <c r="V48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3043,8 +3154,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3219,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,8 +3284,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3184,23 +3304,23 @@
       <c r="G52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H52" s="3">
-        <v>0</v>
+      <c r="H52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J52" s="3">
         <v>100</v>
       </c>
       <c r="K52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L52" s="3">
         <v>200</v>
       </c>
       <c r="M52" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="N52" s="3">
         <v>400</v>
@@ -3220,8 +3340,8 @@
       <c r="S52" s="3">
         <v>400</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>8</v>
+      <c r="T52" s="3">
+        <v>400</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>8</v>
@@ -3229,8 +3349,11 @@
       <c r="V52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,70 +3414,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>15700</v>
+        <v>14300</v>
       </c>
       <c r="E54" s="3">
         <v>15700</v>
       </c>
       <c r="F54" s="3">
+        <v>15700</v>
+      </c>
+      <c r="G54" s="3">
         <v>15600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>18500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>58500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>35000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>33400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>34300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>32100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>33000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>31700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>32200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>32700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>36200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>35300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>40200</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3506,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,8 +3531,9 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3418,53 +3549,56 @@
       <c r="G57" s="3">
         <v>0</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="H57" s="3">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J57" s="3">
         <v>200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>300</v>
       </c>
-      <c r="K57" s="3">
-        <v>100</v>
-      </c>
       <c r="L57" s="3">
+        <v>100</v>
+      </c>
+      <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>200</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3483,20 +3617,20 @@
       <c r="H58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I58" s="3">
-        <v>1500</v>
+      <c r="I58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J58" s="3">
         <v>1500</v>
       </c>
       <c r="K58" s="3">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="L58" s="3">
         <v>2500</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>8</v>
+      <c r="M58" s="3">
+        <v>2500</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>8</v>
@@ -3504,14 +3638,14 @@
       <c r="O58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="P58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -3525,8 +3659,11 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3537,58 +3674,61 @@
         <v>0</v>
       </c>
       <c r="F59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H59" s="3">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
         <v>39500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>700</v>
-      </c>
-      <c r="N59" s="3">
-        <v>500</v>
       </c>
       <c r="O59" s="3">
         <v>500</v>
       </c>
       <c r="P59" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q59" s="3">
         <v>700</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>500</v>
       </c>
       <c r="R59" s="3">
         <v>500</v>
       </c>
       <c r="S59" s="3">
+        <v>500</v>
+      </c>
+      <c r="T59" s="3">
         <v>1100</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3596,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="E60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F60" s="3">
         <v>100</v>
@@ -3605,52 +3745,55 @@
         <v>100</v>
       </c>
       <c r="H60" s="3">
+        <v>100</v>
+      </c>
+      <c r="I60" s="3">
         <v>39500</v>
-      </c>
-      <c r="I60" s="3">
-        <v>2300</v>
       </c>
       <c r="J60" s="3">
         <v>2300</v>
       </c>
       <c r="K60" s="3">
+        <v>2300</v>
+      </c>
+      <c r="L60" s="3">
         <v>3600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>700</v>
-      </c>
-      <c r="P60" s="3">
-        <v>900</v>
       </c>
       <c r="Q60" s="3">
         <v>900</v>
       </c>
       <c r="R60" s="3">
+        <v>900</v>
+      </c>
+      <c r="S60" s="3">
         <v>700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1300</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3670,7 +3813,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
         <v>3500</v>
@@ -3679,40 +3822,43 @@
         <v>3500</v>
       </c>
       <c r="L61" s="3">
+        <v>3500</v>
+      </c>
+      <c r="M61" s="3">
         <v>4000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>9600</v>
-      </c>
-      <c r="N61" s="3">
-        <v>9500</v>
       </c>
       <c r="O61" s="3">
         <v>9500</v>
       </c>
       <c r="P61" s="3">
+        <v>9500</v>
+      </c>
+      <c r="Q61" s="3">
         <v>10000</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>14000</v>
       </c>
       <c r="R61" s="3">
         <v>14000</v>
       </c>
       <c r="S61" s="3">
+        <v>14000</v>
+      </c>
+      <c r="T61" s="3">
         <v>18000</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3723,29 +3869,29 @@
         <v>300</v>
       </c>
       <c r="F62" s="3">
+        <v>300</v>
+      </c>
+      <c r="G62" s="3">
         <v>200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>900</v>
-      </c>
-      <c r="J62" s="3">
-        <v>700</v>
       </c>
       <c r="K62" s="3">
         <v>700</v>
       </c>
       <c r="L62" s="3">
+        <v>700</v>
+      </c>
+      <c r="M62" s="3">
         <v>200</v>
       </c>
-      <c r="M62" s="3">
-        <v>100</v>
-      </c>
       <c r="N62" s="3">
         <v>100</v>
       </c>
@@ -3762,19 +3908,22 @@
         <v>100</v>
       </c>
       <c r="S62" s="3">
+        <v>100</v>
+      </c>
+      <c r="T62" s="3">
         <v>200</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +3984,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4049,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,8 +4114,11 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -3974,55 +4132,58 @@
         <v>300</v>
       </c>
       <c r="G66" s="3">
+        <v>300</v>
+      </c>
+      <c r="H66" s="3">
         <v>500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>40100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>10400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>11100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>15000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>14900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>19500</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4206,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4269,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4334,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4231,8 +4399,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,70 +4464,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>15300</v>
+        <v>13900</v>
       </c>
       <c r="E72" s="3">
         <v>15300</v>
       </c>
       <c r="F72" s="3">
+        <v>15300</v>
+      </c>
+      <c r="G72" s="3">
         <v>15200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>17900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>18300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>28300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>26900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>26500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>24200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>22200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>21100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>21700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>21500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>21100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>20400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>20600</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4594,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4659,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,70 +4724,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>15400</v>
+        <v>14000</v>
       </c>
       <c r="E76" s="3">
         <v>15400</v>
       </c>
       <c r="F76" s="3">
+        <v>15400</v>
+      </c>
+      <c r="G76" s="3">
         <v>15200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>18000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>18400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>28400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>26900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>26500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>24300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>22200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>21200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>21800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>21600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>21200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>20500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>20700</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,75 +4854,81 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44561</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44469</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44377</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44286</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44196</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44104</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44012</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43921</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43830</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43738</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43646</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43555</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43465</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43373</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4741,61 +4936,64 @@
         <v>0</v>
       </c>
       <c r="E81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F81" s="3">
-        <v>-400</v>
+        <v>100</v>
       </c>
       <c r="G81" s="3">
         <v>-400</v>
       </c>
       <c r="H81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I81" s="3">
         <v>113200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1500</v>
       </c>
-      <c r="T81" s="3">
-        <v>100</v>
-      </c>
       <c r="U81" s="3">
+        <v>100</v>
+      </c>
+      <c r="V81" s="3">
         <v>1200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,8 +5016,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4835,29 +5034,29 @@
       <c r="G83" s="3">
         <v>0</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I83" s="3">
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J83" s="3">
         <v>200</v>
       </c>
-      <c r="J83" s="3">
-        <v>100</v>
-      </c>
       <c r="K83" s="3">
+        <v>100</v>
+      </c>
+      <c r="L83" s="3">
         <v>200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>200</v>
       </c>
-      <c r="N83" s="3">
-        <v>100</v>
-      </c>
       <c r="O83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P83" s="3">
         <v>200</v>
@@ -4866,10 +5065,10 @@
         <v>200</v>
       </c>
       <c r="R83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T83" s="3">
         <v>200</v>
@@ -4878,10 +5077,13 @@
         <v>200</v>
       </c>
       <c r="V83" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="W83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5144,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5209,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5274,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5339,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,8 +5404,11 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5199,61 +5416,64 @@
         <v>-100</v>
       </c>
       <c r="E89" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F89" s="3">
+        <v>100</v>
+      </c>
+      <c r="G89" s="3">
         <v>-500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-39300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1100</v>
       </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
       <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3">
         <v>1400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>300</v>
       </c>
-      <c r="O89" s="3">
-        <v>100</v>
-      </c>
       <c r="P89" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q89" s="3">
         <v>1200</v>
       </c>
-      <c r="Q89" s="3">
-        <v>100</v>
-      </c>
       <c r="R89" s="3">
+        <v>100</v>
+      </c>
+      <c r="S89" s="3">
         <v>-700</v>
       </c>
-      <c r="S89" s="3">
-        <v>100</v>
-      </c>
       <c r="T89" s="3">
+        <v>100</v>
+      </c>
+      <c r="U89" s="3">
         <v>-100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,38 +5496,39 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1500</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-5200</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
@@ -5330,16 +5551,19 @@
         <v>0</v>
       </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5624,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,70 +5689,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1500</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>172600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>2700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1600</v>
-      </c>
-      <c r="M94" s="3">
-        <v>200</v>
       </c>
       <c r="N94" s="3">
         <v>200</v>
       </c>
       <c r="O94" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P94" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q94" s="3">
+        <v>100</v>
+      </c>
+      <c r="R94" s="3">
         <v>4400</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>3200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>1200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,8 +5781,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5566,11 +5800,11 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>-119200</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
@@ -5610,8 +5844,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +5909,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +5974,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,70 +6039,76 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-100</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-2300</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-125700</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-1000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4600</v>
       </c>
-      <c r="M100" s="3">
-        <v>100</v>
-      </c>
       <c r="N100" s="3">
+        <v>100</v>
+      </c>
+      <c r="O100" s="3">
         <v>-500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-4000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-400</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5920,66 +6169,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1600</v>
       </c>
-      <c r="E102" s="3">
-        <v>100</v>
-      </c>
       <c r="F102" s="3">
+        <v>100</v>
+      </c>
+      <c r="G102" s="3">
         <v>-2900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-39300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>50700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1400</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>-700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>4700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-4700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KEWL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KEWL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="92">
   <si>
     <t>KEWL</t>
   </si>
@@ -663,11 +663,11 @@
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -699,22 +699,22 @@
         <v>45473</v>
       </c>
       <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J7" s="2">
         <v>44926</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I7" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J7" s="2">
-        <v>44469</v>
       </c>
       <c r="K7" s="2">
         <v>44377</v>
@@ -760,11 +760,11 @@
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>100</v>
+      <c r="D8" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F8" s="3">
         <v>100</v>
@@ -773,13 +773,13 @@
         <v>100</v>
       </c>
       <c r="H8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J8" s="3">
-        <v>6400</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3">
         <v>3500</v>
@@ -829,7 +829,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3">
         <v>100</v>
@@ -838,13 +838,13 @@
         <v>100</v>
       </c>
       <c r="H9" s="3">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>8</v>
+        <v>100</v>
+      </c>
+      <c r="I9" s="3">
+        <v>100</v>
       </c>
       <c r="J9" s="3">
-        <v>3900</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3">
         <v>2500</v>
@@ -903,13 +903,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="3">
-        <v>200</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
       </c>
       <c r="J10" s="3">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3">
         <v>1000</v>
@@ -1110,26 +1110,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>-200</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1263,25 +1263,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E17" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F17" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G17" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="H17" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="I17" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J17" s="3">
-        <v>4400</v>
+        <v>200</v>
       </c>
       <c r="K17" s="3">
         <v>3100</v>
@@ -1328,25 +1328,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J18" s="3">
         <v>-200</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-200</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-300</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-300</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I18" s="3">
-        <v>100</v>
-      </c>
-      <c r="J18" s="3">
-        <v>2000</v>
       </c>
       <c r="K18" s="3">
         <v>400</v>
@@ -1417,26 +1417,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>200</v>
-      </c>
-      <c r="E20" s="3">
-        <v>200</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F20" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+        <v>-100</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1483,25 +1483,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F21" s="3">
-        <v>200</v>
+        <v>-400</v>
       </c>
       <c r="G21" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
         <v>-200</v>
-      </c>
-      <c r="I21" s="3">
-        <v>300</v>
-      </c>
-      <c r="J21" s="3">
-        <v>2200</v>
       </c>
       <c r="K21" s="3">
         <v>600</v>
@@ -1565,8 +1565,8 @@
       <c r="I22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K22" s="3">
         <v>100</v>
@@ -1619,19 +1619,19 @@
         <v>0</v>
       </c>
       <c r="F23" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G23" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="H23" s="3">
+        <v>100</v>
+      </c>
+      <c r="I23" s="3">
+        <v>100</v>
+      </c>
+      <c r="J23" s="3">
         <v>-200</v>
-      </c>
-      <c r="I23" s="3">
-        <v>100</v>
-      </c>
-      <c r="J23" s="3">
-        <v>2000</v>
       </c>
       <c r="K23" s="3">
         <v>400</v>
@@ -1687,16 +1687,16 @@
         <v>0</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>-100</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>500</v>
       </c>
       <c r="K24" s="3">
         <v>100</v>
@@ -1814,19 +1814,19 @@
         <v>0</v>
       </c>
       <c r="F26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
+        <v>100</v>
+      </c>
+      <c r="I26" s="3">
+        <v>100</v>
+      </c>
+      <c r="J26" s="3">
         <v>-200</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I26" s="3">
-        <v>100</v>
-      </c>
-      <c r="J26" s="3">
-        <v>1500</v>
       </c>
       <c r="K26" s="3">
         <v>300</v>
@@ -1879,19 +1879,19 @@
         <v>0</v>
       </c>
       <c r="F27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
+        <v>100</v>
+      </c>
+      <c r="I27" s="3">
+        <v>100</v>
+      </c>
+      <c r="J27" s="3">
         <v>-200</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I27" s="3">
-        <v>100</v>
-      </c>
-      <c r="J27" s="3">
-        <v>1500</v>
       </c>
       <c r="K27" s="3">
         <v>300</v>
@@ -2002,8 +2002,8 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -2012,16 +2012,16 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>113100</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>-100</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -2197,26 +2197,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-200</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F32" s="3">
-        <v>-500</v>
+        <v>-300</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2269,19 +2269,19 @@
         <v>0</v>
       </c>
       <c r="F33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G33" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="H33" s="3">
-        <v>-400</v>
+        <v>100</v>
       </c>
       <c r="I33" s="3">
-        <v>113200</v>
+        <v>100</v>
       </c>
       <c r="J33" s="3">
-        <v>1500</v>
+        <v>-200</v>
       </c>
       <c r="K33" s="3">
         <v>300</v>
@@ -2399,19 +2399,19 @@
         <v>0</v>
       </c>
       <c r="F35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G35" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="H35" s="3">
-        <v>-400</v>
+        <v>100</v>
       </c>
       <c r="I35" s="3">
-        <v>113200</v>
+        <v>100</v>
       </c>
       <c r="J35" s="3">
-        <v>1500</v>
+        <v>-200</v>
       </c>
       <c r="K35" s="3">
         <v>300</v>
@@ -2466,22 +2466,22 @@
         <v>45473</v>
       </c>
       <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J38" s="2">
         <v>44926</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I38" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J38" s="2">
-        <v>44469</v>
       </c>
       <c r="K38" s="2">
         <v>44377</v>
@@ -2581,22 +2581,22 @@
         <v>4000</v>
       </c>
       <c r="E41" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F41" s="3">
         <v>8400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
+        <v>8400</v>
+      </c>
+      <c r="H41" s="3">
         <v>10100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
+        <v>10100</v>
+      </c>
+      <c r="J41" s="3">
         <v>9900</v>
-      </c>
-      <c r="H41" s="3">
-        <v>3600</v>
-      </c>
-      <c r="I41" s="3">
-        <v>41900</v>
-      </c>
-      <c r="J41" s="3">
-        <v>1200</v>
       </c>
       <c r="K41" s="3">
         <v>1800</v>
@@ -2708,25 +2708,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F43" s="3">
         <v>100</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H43" s="3">
         <v>100</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>8</v>
+      <c r="I43" s="3">
+        <v>100</v>
       </c>
       <c r="J43" s="3">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="K43" s="3">
         <v>1400</v>
@@ -2790,8 +2790,8 @@
       <c r="I44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J44" s="3">
-        <v>200</v>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>200</v>
@@ -2838,25 +2838,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
-        <v>9300</v>
-      </c>
-      <c r="I45" s="3">
-        <v>11100</v>
-      </c>
-      <c r="J45" s="3">
-        <v>200</v>
+        <v>100</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K45" s="3">
         <v>2800</v>
@@ -2906,22 +2906,22 @@
         <v>4200</v>
       </c>
       <c r="E46" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F46" s="3">
         <v>8600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
+        <v>8600</v>
+      </c>
+      <c r="H46" s="3">
         <v>10200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
+        <v>10200</v>
+      </c>
+      <c r="J46" s="3">
         <v>10000</v>
-      </c>
-      <c r="H46" s="3">
-        <v>13000</v>
-      </c>
-      <c r="I46" s="3">
-        <v>53000</v>
-      </c>
-      <c r="J46" s="3">
-        <v>2900</v>
       </c>
       <c r="K46" s="3">
         <v>6100</v>
@@ -2970,8 +2970,8 @@
       <c r="D47" s="3">
         <v>2000</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>8</v>
+      <c r="E47" s="3">
+        <v>2000</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>8</v>
@@ -3036,22 +3036,22 @@
         <v>8100</v>
       </c>
       <c r="E48" s="3">
+        <v>8100</v>
+      </c>
+      <c r="F48" s="3">
         <v>7100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
+        <v>7100</v>
+      </c>
+      <c r="H48" s="3">
         <v>5600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>5600</v>
       </c>
-      <c r="H48" s="3">
-        <v>5500</v>
-      </c>
-      <c r="I48" s="3">
-        <v>5500</v>
-      </c>
       <c r="J48" s="3">
-        <v>32100</v>
+        <v>5600</v>
       </c>
       <c r="K48" s="3">
         <v>27200</v>
@@ -3307,11 +3307,11 @@
       <c r="H52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>100</v>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K52" s="3">
         <v>100</v>
@@ -3426,22 +3426,22 @@
         <v>14300</v>
       </c>
       <c r="E54" s="3">
-        <v>15700</v>
+        <v>14300</v>
       </c>
       <c r="F54" s="3">
         <v>15700</v>
       </c>
       <c r="G54" s="3">
+        <v>15700</v>
+      </c>
+      <c r="H54" s="3">
+        <v>15700</v>
+      </c>
+      <c r="I54" s="3">
+        <v>15700</v>
+      </c>
+      <c r="J54" s="3">
         <v>15600</v>
-      </c>
-      <c r="H54" s="3">
-        <v>18500</v>
-      </c>
-      <c r="I54" s="3">
-        <v>58500</v>
-      </c>
-      <c r="J54" s="3">
-        <v>35000</v>
       </c>
       <c r="K54" s="3">
         <v>33400</v>
@@ -3552,11 +3552,11 @@
       <c r="H57" s="3">
         <v>0</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>8</v>
+      <c r="I57" s="3">
+        <v>0</v>
       </c>
       <c r="J57" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K57" s="3">
         <v>300</v>
@@ -3602,26 +3602,26 @@
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>8</v>
+      <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3">
         <v>1500</v>
@@ -3667,26 +3667,26 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
-      </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3">
-        <v>100</v>
-      </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
-        <v>39500</v>
-      </c>
-      <c r="J59" s="3">
-        <v>600</v>
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K59" s="3">
         <v>500</v>
@@ -3739,19 +3739,19 @@
         <v>0</v>
       </c>
       <c r="F60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H60" s="3">
         <v>100</v>
       </c>
       <c r="I60" s="3">
-        <v>39500</v>
+        <v>100</v>
       </c>
       <c r="J60" s="3">
-        <v>2300</v>
+        <v>100</v>
       </c>
       <c r="K60" s="3">
         <v>2300</v>
@@ -3816,7 +3816,7 @@
         <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3">
         <v>3500</v>
@@ -3862,26 +3862,26 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>300</v>
-      </c>
-      <c r="E62" s="3">
-        <v>300</v>
-      </c>
-      <c r="F62" s="3">
-        <v>300</v>
-      </c>
-      <c r="G62" s="3">
-        <v>200</v>
-      </c>
-      <c r="H62" s="3">
-        <v>400</v>
-      </c>
-      <c r="I62" s="3">
-        <v>500</v>
-      </c>
-      <c r="J62" s="3">
-        <v>900</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K62" s="3">
         <v>700</v>
@@ -4135,13 +4135,13 @@
         <v>300</v>
       </c>
       <c r="H66" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="I66" s="3">
-        <v>40100</v>
+        <v>300</v>
       </c>
       <c r="J66" s="3">
-        <v>6600</v>
+        <v>300</v>
       </c>
       <c r="K66" s="3">
         <v>6500</v>
@@ -4476,22 +4476,22 @@
         <v>13900</v>
       </c>
       <c r="E72" s="3">
-        <v>15300</v>
+        <v>13900</v>
       </c>
       <c r="F72" s="3">
         <v>15300</v>
       </c>
       <c r="G72" s="3">
+        <v>15300</v>
+      </c>
+      <c r="H72" s="3">
+        <v>15300</v>
+      </c>
+      <c r="I72" s="3">
+        <v>15300</v>
+      </c>
+      <c r="J72" s="3">
         <v>15200</v>
-      </c>
-      <c r="H72" s="3">
-        <v>17900</v>
-      </c>
-      <c r="I72" s="3">
-        <v>18300</v>
-      </c>
-      <c r="J72" s="3">
-        <v>28300</v>
       </c>
       <c r="K72" s="3">
         <v>26900</v>
@@ -4736,22 +4736,22 @@
         <v>14000</v>
       </c>
       <c r="E76" s="3">
-        <v>15400</v>
+        <v>14000</v>
       </c>
       <c r="F76" s="3">
         <v>15400</v>
       </c>
       <c r="G76" s="3">
+        <v>15400</v>
+      </c>
+      <c r="H76" s="3">
+        <v>15400</v>
+      </c>
+      <c r="I76" s="3">
+        <v>15400</v>
+      </c>
+      <c r="J76" s="3">
         <v>15200</v>
-      </c>
-      <c r="H76" s="3">
-        <v>18000</v>
-      </c>
-      <c r="I76" s="3">
-        <v>18400</v>
-      </c>
-      <c r="J76" s="3">
-        <v>28400</v>
       </c>
       <c r="K76" s="3">
         <v>26900</v>
@@ -4871,22 +4871,22 @@
         <v>45473</v>
       </c>
       <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J80" s="2">
         <v>44926</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I80" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J80" s="2">
-        <v>44469</v>
       </c>
       <c r="K80" s="2">
         <v>44377</v>
@@ -4939,19 +4939,19 @@
         <v>0</v>
       </c>
       <c r="F81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G81" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="H81" s="3">
-        <v>-400</v>
+        <v>100</v>
       </c>
       <c r="I81" s="3">
-        <v>113200</v>
+        <v>100</v>
       </c>
       <c r="J81" s="3">
-        <v>1500</v>
+        <v>-200</v>
       </c>
       <c r="K81" s="3">
         <v>300</v>
@@ -5037,11 +5037,11 @@
       <c r="H83" s="3">
         <v>0</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J83" s="3">
-        <v>200</v>
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K83" s="3">
         <v>100</v>
@@ -5413,25 +5413,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G89" s="3">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="H89" s="3">
-        <v>-39300</v>
+        <v>0</v>
       </c>
       <c r="I89" s="3">
-        <v>3900</v>
+        <v>0</v>
       </c>
       <c r="J89" s="3">
-        <v>1100</v>
+        <v>-200</v>
       </c>
       <c r="K89" s="3">
         <v>0</v>
@@ -5503,22 +5503,22 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1000</v>
+        <v>-500</v>
       </c>
       <c r="E91" s="3">
-        <v>-1500</v>
+        <v>-500</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="G91" s="3">
-        <v>-100</v>
+        <v>-800</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
       <c r="I91" s="3">
-        <v>-5200</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -5698,25 +5698,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-3000</v>
+        <v>-1500</v>
       </c>
       <c r="E94" s="3">
         <v>-1500</v>
       </c>
       <c r="F94" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="G94" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-100</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>172600</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-4300</v>
       </c>
       <c r="K94" s="3">
         <v>300</v>
@@ -5787,26 +5787,26 @@
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-119200</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6048,25 +6048,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1400</v>
+        <v>-700</v>
       </c>
       <c r="E100" s="3">
-        <v>-100</v>
+        <v>-700</v>
       </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J100" s="3">
         <v>-2300</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-125700</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
       </c>
       <c r="K100" s="3">
         <v>-1000</v>
@@ -6112,26 +6112,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6178,25 +6178,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-4500</v>
+        <v>-2200</v>
       </c>
       <c r="E102" s="3">
-        <v>-1600</v>
+        <v>-2200</v>
       </c>
       <c r="F102" s="3">
-        <v>100</v>
+        <v>-800</v>
       </c>
       <c r="G102" s="3">
-        <v>-2900</v>
+        <v>-800</v>
       </c>
       <c r="H102" s="3">
-        <v>-39300</v>
+        <v>100</v>
       </c>
       <c r="I102" s="3">
-        <v>50700</v>
+        <v>100</v>
       </c>
       <c r="J102" s="3">
-        <v>-3200</v>
+        <v>-2600</v>
       </c>
       <c r="K102" s="3">
         <v>-700</v>

--- a/AAII_Financials/Quarterly/KEWL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KEWL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="92">
   <si>
     <t>KEWL</t>
   </si>
@@ -656,112 +656,119 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>8</v>
+      <c r="D8" s="3">
+        <v>100</v>
       </c>
       <c r="E8" s="3">
         <v>100</v>
@@ -779,49 +786,55 @@
         <v>100</v>
       </c>
       <c r="J8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K8" s="3">
+        <v>100</v>
+      </c>
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
         <v>3500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>7700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>5400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>2300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>6100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>4700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>9500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>5500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>3500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>6200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -832,10 +845,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H9" s="3">
         <v>100</v>
@@ -844,49 +857,55 @@
         <v>100</v>
       </c>
       <c r="J9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K9" s="3">
+        <v>100</v>
+      </c>
+      <c r="L9" s="3">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3">
         <v>2500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>4000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>3600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>3700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>1900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>4700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>3700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>8100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>1400</v>
-      </c>
-      <c r="T9" s="3">
-        <v>4000</v>
-      </c>
-      <c r="U9" s="3">
-        <v>3000</v>
       </c>
       <c r="V9" s="3">
         <v>4000</v>
       </c>
       <c r="W9" s="3">
+        <v>3000</v>
+      </c>
+      <c r="X9" s="3">
+        <v>4000</v>
+      </c>
+      <c r="Y9" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -897,10 +916,10 @@
         <v>100</v>
       </c>
       <c r="F10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10" s="3">
         <v>0</v>
@@ -912,46 +931,52 @@
         <v>0</v>
       </c>
       <c r="K10" s="3">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3">
         <v>1000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>3700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>-3400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>400</v>
-      </c>
-      <c r="P10" s="3">
-        <v>1400</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>1000</v>
       </c>
       <c r="R10" s="3">
         <v>1400</v>
       </c>
       <c r="S10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T10" s="3">
+        <v>1400</v>
+      </c>
+      <c r="U10" s="3">
         <v>300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>1500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>2200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -975,8 +1000,10 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1040,8 +1067,14 @@
       <c r="W12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1105,28 +1138,34 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="D14" s="3">
         <v>-200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="E14" s="3">
         <v>-200</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-200</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
@@ -1137,11 +1176,11 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1150,28 +1189,34 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>200</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1235,8 +1280,14 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1257,8 +1308,10 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1284,46 +1337,52 @@
         <v>200</v>
       </c>
       <c r="K17" s="3">
+        <v>200</v>
+      </c>
+      <c r="L17" s="3">
+        <v>200</v>
+      </c>
+      <c r="M17" s="3">
         <v>3100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>4600</v>
       </c>
-      <c r="M17" s="3">
-        <v>100</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
+        <v>100</v>
+      </c>
+      <c r="P17" s="3">
         <v>4100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>2300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>5200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>4100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>8700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>4900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>3400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>4800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1346,49 +1405,55 @@
         <v>-100</v>
       </c>
       <c r="J18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L18" s="3">
         <v>-200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>3100</v>
       </c>
-      <c r="M18" s="3">
-        <v>100</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
+        <v>100</v>
+      </c>
+      <c r="P18" s="3">
         <v>1300</v>
       </c>
-      <c r="O18" s="3">
-        <v>0</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
+        <v>0</v>
+      </c>
+      <c r="R18" s="3">
         <v>900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>600</v>
       </c>
-      <c r="U18" s="3">
-        <v>100</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
+        <v>100</v>
+      </c>
+      <c r="X18" s="3">
         <v>1400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1412,8 +1477,10 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1423,35 +1490,35 @@
       <c r="E20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="3">
-        <v>300</v>
-      </c>
-      <c r="G20" s="3">
-        <v>300</v>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H20" s="3">
+        <v>200</v>
+      </c>
+      <c r="I20" s="3">
+        <v>200</v>
+      </c>
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
@@ -1466,19 +1533,25 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>1500</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1489,61 +1562,67 @@
         <v>-100</v>
       </c>
       <c r="F21" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="G21" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="H21" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="I21" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
         <v>-200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>3300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>1000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>1500</v>
       </c>
-      <c r="O21" s="3">
-        <v>100</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
+        <v>100</v>
+      </c>
+      <c r="R21" s="3">
         <v>1100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>1000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>2400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>1600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1568,17 +1647,17 @@
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
-        <v>100</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M22" s="3">
         <v>100</v>
       </c>
       <c r="N22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O22" s="3">
         <v>100</v>
@@ -1593,10 +1672,10 @@
         <v>100</v>
       </c>
       <c r="S22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U22" s="3">
         <v>200</v>
@@ -1607,16 +1686,22 @@
       <c r="W22" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E23" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F23" s="3">
         <v>0</v>
@@ -1625,55 +1710,61 @@
         <v>0</v>
       </c>
       <c r="H23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3">
+        <v>100</v>
+      </c>
+      <c r="K23" s="3">
+        <v>100</v>
+      </c>
+      <c r="L23" s="3">
         <v>-200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>3100</v>
       </c>
-      <c r="M23" s="3">
-        <v>100</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
+        <v>100</v>
+      </c>
+      <c r="P23" s="3">
         <v>1200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>2000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>1200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1696,49 +1787,55 @@
         <v>0</v>
       </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="K24" s="3">
-        <v>100</v>
-      </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
+        <v>100</v>
+      </c>
+      <c r="N24" s="3">
         <v>800</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>200</v>
-      </c>
       <c r="Q24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R24" s="3">
         <v>200</v>
       </c>
       <c r="S24" s="3">
+        <v>100</v>
+      </c>
+      <c r="T24" s="3">
+        <v>200</v>
+      </c>
+      <c r="U24" s="3">
         <v>-100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-200</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1802,16 +1899,22 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F26" s="3">
         <v>0</v>
@@ -1820,63 +1923,69 @@
         <v>0</v>
       </c>
       <c r="H26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J26" s="3">
+        <v>100</v>
+      </c>
+      <c r="K26" s="3">
+        <v>100</v>
+      </c>
+      <c r="L26" s="3">
         <v>-200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>2300</v>
       </c>
-      <c r="M26" s="3">
-        <v>100</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
+        <v>100</v>
+      </c>
+      <c r="P26" s="3">
         <v>900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>1500</v>
       </c>
-      <c r="U26" s="3">
-        <v>100</v>
-      </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
+        <v>100</v>
+      </c>
+      <c r="X26" s="3">
         <v>1200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F27" s="3">
         <v>0</v>
@@ -1885,55 +1994,61 @@
         <v>0</v>
       </c>
       <c r="H27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J27" s="3">
+        <v>100</v>
+      </c>
+      <c r="K27" s="3">
+        <v>100</v>
+      </c>
+      <c r="L27" s="3">
         <v>-200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>2300</v>
       </c>
-      <c r="M27" s="3">
-        <v>100</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
+        <v>100</v>
+      </c>
+      <c r="P27" s="3">
         <v>900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>1500</v>
       </c>
-      <c r="U27" s="3">
-        <v>100</v>
-      </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
+        <v>100</v>
+      </c>
+      <c r="X27" s="3">
         <v>1200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1997,8 +2112,14 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2021,28 +2142,28 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-100</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M29" s="3">
+      <c r="M29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O29" s="3">
         <v>3300</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -2062,8 +2183,14 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2127,8 +2254,14 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2192,8 +2325,14 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2203,36 +2342,36 @@
       <c r="E32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-300</v>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H32" s="3">
-        <v>100</v>
+        <v>-200</v>
       </c>
       <c r="I32" s="3">
-        <v>100</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>8</v>
+        <v>-200</v>
+      </c>
+      <c r="J32" s="3">
+        <v>100</v>
       </c>
       <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2246,27 +2385,33 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-1500</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F33" s="3">
         <v>0</v>
@@ -2275,55 +2420,61 @@
         <v>0</v>
       </c>
       <c r="H33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J33" s="3">
+        <v>100</v>
+      </c>
+      <c r="K33" s="3">
+        <v>100</v>
+      </c>
+      <c r="L33" s="3">
         <v>-200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>2300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>3400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>1500</v>
       </c>
-      <c r="U33" s="3">
-        <v>100</v>
-      </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
+        <v>100</v>
+      </c>
+      <c r="X33" s="3">
         <v>1200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2387,16 +2538,22 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F35" s="3">
         <v>0</v>
@@ -2405,125 +2562,137 @@
         <v>0</v>
       </c>
       <c r="H35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J35" s="3">
+        <v>100</v>
+      </c>
+      <c r="K35" s="3">
+        <v>100</v>
+      </c>
+      <c r="L35" s="3">
         <v>-200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>2300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>3400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>1500</v>
       </c>
-      <c r="U35" s="3">
-        <v>100</v>
-      </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
+        <v>100</v>
+      </c>
+      <c r="X35" s="3">
         <v>1200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2547,8 +2716,10 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2572,73 +2743,81 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F41" s="3">
         <v>4000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>4000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>8400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>8400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>10100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>10100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>9900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>3100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>2400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>5700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>5600</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2702,8 +2881,14 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2726,49 +2911,55 @@
         <v>100</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K43" s="3">
+        <v>100</v>
+      </c>
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
         <v>1400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>2000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>900</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2793,47 +2984,53 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M44" s="3">
         <v>200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>300</v>
       </c>
-      <c r="O44" s="3">
-        <v>100</v>
-      </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
+        <v>100</v>
+      </c>
+      <c r="R44" s="3">
         <v>200</v>
       </c>
-      <c r="Q44" s="3">
-        <v>100</v>
-      </c>
-      <c r="R44" s="3">
-        <v>100</v>
-      </c>
       <c r="S44" s="3">
         <v>100</v>
       </c>
       <c r="T44" s="3">
         <v>100</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V44" s="3" t="s">
-        <v>8</v>
+      <c r="U44" s="3">
+        <v>100</v>
+      </c>
+      <c r="V44" s="3">
+        <v>100</v>
       </c>
       <c r="W44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2849,38 +3046,38 @@
       <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>8</v>
+      <c r="H45" s="3">
+        <v>100</v>
+      </c>
+      <c r="I45" s="3">
+        <v>100</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>2800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>2700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>300</v>
-      </c>
-      <c r="N45" s="3">
-        <v>600</v>
-      </c>
-      <c r="O45" s="3">
-        <v>600</v>
       </c>
       <c r="P45" s="3">
         <v>600</v>
       </c>
       <c r="Q45" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="R45" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="S45" s="3">
         <v>400</v>
@@ -2888,82 +3085,94 @@
       <c r="T45" s="3">
         <v>400</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V45" s="3" t="s">
-        <v>8</v>
+      <c r="U45" s="3">
+        <v>400</v>
+      </c>
+      <c r="V45" s="3">
+        <v>400</v>
       </c>
       <c r="W45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F46" s="3">
         <v>4200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>4200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>8600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>8600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>10200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>10200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>10000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>6100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>7000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>4200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>4900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>3400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>3800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>4100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>7600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>2200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>7000</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2973,11 +3182,11 @@
       <c r="E47" s="3">
         <v>2000</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>8</v>
+      <c r="F47" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G47" s="3">
+        <v>2000</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>8</v>
@@ -2988,11 +3197,11 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3027,73 +3236,85 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>8300</v>
+      </c>
+      <c r="F48" s="3">
         <v>8100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>8100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>7100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>7100</v>
-      </c>
-      <c r="H48" s="3">
-        <v>5600</v>
-      </c>
-      <c r="I48" s="3">
-        <v>5600</v>
       </c>
       <c r="J48" s="3">
         <v>5600</v>
       </c>
       <c r="K48" s="3">
+        <v>5600</v>
+      </c>
+      <c r="L48" s="3">
+        <v>5600</v>
+      </c>
+      <c r="M48" s="3">
         <v>27200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>27200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>27700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>27700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>27900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>28000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>28200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>28300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>32800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>32800</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3157,8 +3378,14 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3222,8 +3449,14 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3287,8 +3520,14 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3313,20 +3552,20 @@
       <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K52" s="3">
-        <v>100</v>
-      </c>
-      <c r="L52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M52" s="3">
+        <v>100</v>
+      </c>
+      <c r="N52" s="3">
         <v>200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>200</v>
-      </c>
-      <c r="N52" s="3">
-        <v>400</v>
-      </c>
-      <c r="O52" s="3">
-        <v>400</v>
       </c>
       <c r="P52" s="3">
         <v>400</v>
@@ -3343,17 +3582,23 @@
       <c r="T52" s="3">
         <v>400</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V52" s="3" t="s">
-        <v>8</v>
+      <c r="U52" s="3">
+        <v>400</v>
+      </c>
+      <c r="V52" s="3">
+        <v>400</v>
       </c>
       <c r="W52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3417,22 +3662,28 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>14700</v>
+      </c>
+      <c r="F54" s="3">
         <v>14300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>14300</v>
-      </c>
-      <c r="F54" s="3">
-        <v>15700</v>
-      </c>
-      <c r="G54" s="3">
-        <v>15700</v>
       </c>
       <c r="H54" s="3">
         <v>15700</v>
@@ -3441,49 +3692,55 @@
         <v>15700</v>
       </c>
       <c r="J54" s="3">
+        <v>15700</v>
+      </c>
+      <c r="K54" s="3">
+        <v>15700</v>
+      </c>
+      <c r="L54" s="3">
         <v>15600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>33400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>34300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>32100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>33000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>31700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>32200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>32700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>36200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>35300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>40200</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3507,8 +3764,10 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3532,8 +3791,10 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3559,46 +3820,52 @@
         <v>0</v>
       </c>
       <c r="K57" s="3">
+        <v>0</v>
+      </c>
+      <c r="L57" s="3">
+        <v>0</v>
+      </c>
+      <c r="M57" s="3">
         <v>300</v>
       </c>
-      <c r="L57" s="3">
-        <v>100</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
+        <v>100</v>
+      </c>
+      <c r="O57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>400</v>
-      </c>
-      <c r="O57" s="3">
-        <v>300</v>
-      </c>
-      <c r="P57" s="3">
-        <v>200</v>
       </c>
       <c r="Q57" s="3">
         <v>300</v>
       </c>
       <c r="R57" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="S57" s="3">
         <v>300</v>
       </c>
       <c r="T57" s="3">
+        <v>400</v>
+      </c>
+      <c r="U57" s="3">
+        <v>300</v>
+      </c>
+      <c r="V57" s="3">
         <v>200</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3624,25 +3891,25 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>1500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>2500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>2500</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>8</v>
@@ -3650,8 +3917,8 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="T58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -3662,16 +3929,22 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>8</v>
+      <c r="D59" s="3">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3">
+        <v>0</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>8</v>
@@ -3688,47 +3961,53 @@
       <c r="J59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M59" s="3">
         <v>500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>500</v>
-      </c>
-      <c r="P59" s="3">
-        <v>500</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>700</v>
       </c>
       <c r="R59" s="3">
         <v>500</v>
       </c>
       <c r="S59" s="3">
+        <v>700</v>
+      </c>
+      <c r="T59" s="3">
         <v>500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
+        <v>500</v>
+      </c>
+      <c r="V59" s="3">
         <v>1100</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3745,55 +4024,61 @@
         <v>0</v>
       </c>
       <c r="H60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J60" s="3">
         <v>100</v>
       </c>
       <c r="K60" s="3">
+        <v>100</v>
+      </c>
+      <c r="L60" s="3">
+        <v>100</v>
+      </c>
+      <c r="M60" s="3">
         <v>2300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>3600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>3800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1300</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3819,46 +4104,52 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>3500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>3500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>4000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>9600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>9500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>9500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>10000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>14000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>14000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>18000</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3883,21 +4174,21 @@
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M62" s="3">
         <v>700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>200</v>
       </c>
-      <c r="N62" s="3">
-        <v>100</v>
-      </c>
-      <c r="O62" s="3">
-        <v>100</v>
-      </c>
       <c r="P62" s="3">
         <v>100</v>
       </c>
@@ -3911,19 +4202,25 @@
         <v>100</v>
       </c>
       <c r="T62" s="3">
+        <v>100</v>
+      </c>
+      <c r="U62" s="3">
+        <v>100</v>
+      </c>
+      <c r="V62" s="3">
         <v>200</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3987,8 +4284,14 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4052,8 +4355,14 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4117,16 +4426,22 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E66" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F66" s="3">
         <v>300</v>
@@ -4144,46 +4459,52 @@
         <v>300</v>
       </c>
       <c r="K66" s="3">
+        <v>300</v>
+      </c>
+      <c r="L66" s="3">
+        <v>300</v>
+      </c>
+      <c r="M66" s="3">
         <v>6500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>7700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>7900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>10800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>10500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>10400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>11100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>15000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>14900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>19500</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4207,8 +4528,10 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4272,8 +4595,14 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4337,8 +4666,14 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4402,8 +4737,14 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4467,22 +4808,28 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>14100</v>
+      </c>
+      <c r="F72" s="3">
         <v>13900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>13900</v>
-      </c>
-      <c r="F72" s="3">
-        <v>15300</v>
-      </c>
-      <c r="G72" s="3">
-        <v>15300</v>
       </c>
       <c r="H72" s="3">
         <v>15300</v>
@@ -4491,49 +4838,55 @@
         <v>15300</v>
       </c>
       <c r="J72" s="3">
+        <v>15300</v>
+      </c>
+      <c r="K72" s="3">
+        <v>15300</v>
+      </c>
+      <c r="L72" s="3">
         <v>15200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>26900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>26500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>24200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>22200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>21100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>21700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>21500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>21100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>20400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>20600</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4597,8 +4950,14 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4662,8 +5021,14 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4727,22 +5092,28 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>14300</v>
+      </c>
+      <c r="F76" s="3">
         <v>14000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>14000</v>
-      </c>
-      <c r="F76" s="3">
-        <v>15400</v>
-      </c>
-      <c r="G76" s="3">
-        <v>15400</v>
       </c>
       <c r="H76" s="3">
         <v>15400</v>
@@ -4751,49 +5122,55 @@
         <v>15400</v>
       </c>
       <c r="J76" s="3">
+        <v>15400</v>
+      </c>
+      <c r="K76" s="3">
+        <v>15400</v>
+      </c>
+      <c r="L76" s="3">
         <v>15200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>26900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>26500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>24300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>22200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>21200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>21800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>21600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>21200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>20500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>20700</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4857,86 +5234,98 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F81" s="3">
         <v>0</v>
@@ -4945,55 +5334,61 @@
         <v>0</v>
       </c>
       <c r="H81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J81" s="3">
+        <v>100</v>
+      </c>
+      <c r="K81" s="3">
+        <v>100</v>
+      </c>
+      <c r="L81" s="3">
         <v>-200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>2300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>3400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>1500</v>
       </c>
-      <c r="U81" s="3">
-        <v>100</v>
-      </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
+        <v>100</v>
+      </c>
+      <c r="X81" s="3">
         <v>1200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5017,8 +5412,10 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5040,50 +5437,56 @@
       <c r="I83" s="3">
         <v>0</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>8</v>
+      <c r="J83" s="3">
+        <v>0</v>
       </c>
       <c r="K83" s="3">
-        <v>100</v>
-      </c>
-      <c r="L83" s="3">
-        <v>200</v>
+        <v>0</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M83" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="N83" s="3">
         <v>200</v>
       </c>
       <c r="O83" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="P83" s="3">
         <v>200</v>
       </c>
       <c r="Q83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R83" s="3">
         <v>200</v>
       </c>
       <c r="S83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T83" s="3">
         <v>200</v>
       </c>
       <c r="U83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V83" s="3">
         <v>200</v>
       </c>
       <c r="W83" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="X83" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5147,8 +5550,14 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5212,8 +5621,14 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5277,8 +5692,14 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5342,8 +5763,14 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5407,16 +5834,22 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F89" s="3">
         <v>0</v>
@@ -5431,49 +5864,55 @@
         <v>0</v>
       </c>
       <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3">
         <v>-200</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3">
         <v>1400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>300</v>
       </c>
-      <c r="P89" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
+        <v>100</v>
+      </c>
+      <c r="S89" s="3">
         <v>1200</v>
       </c>
-      <c r="R89" s="3">
-        <v>100</v>
-      </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
+        <v>100</v>
+      </c>
+      <c r="U89" s="3">
         <v>-700</v>
       </c>
-      <c r="T89" s="3">
-        <v>100</v>
-      </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
+        <v>100</v>
+      </c>
+      <c r="W89" s="3">
         <v>-100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5497,29 +5936,31 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-800</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
@@ -5527,14 +5968,14 @@
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
@@ -5554,16 +5995,22 @@
         <v>0</v>
       </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5627,8 +6074,14 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5692,73 +6145,85 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-1500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-800</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>2700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>1600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>200</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>100</v>
-      </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
+        <v>100</v>
+      </c>
+      <c r="T94" s="3">
         <v>4400</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>3200</v>
-      </c>
-      <c r="U94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="V94" s="3">
-        <v>1200</v>
       </c>
       <c r="W94" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Y94" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5782,8 +6247,10 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5808,11 +6275,11 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5847,8 +6314,14 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5912,8 +6385,14 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5977,8 +6456,14 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6042,73 +6527,85 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-700</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L100" s="3">
         <v>-2300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-1000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-4600</v>
       </c>
-      <c r="N100" s="3">
-        <v>100</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-4100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-4000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-400</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6133,11 +6630,11 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6172,69 +6669,81 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-2200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-2200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-800</v>
       </c>
-      <c r="H102" s="3">
-        <v>100</v>
-      </c>
-      <c r="I102" s="3">
-        <v>100</v>
-      </c>
       <c r="J102" s="3">
+        <v>100</v>
+      </c>
+      <c r="K102" s="3">
+        <v>100</v>
+      </c>
+      <c r="L102" s="3">
         <v>-2600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>3600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-1100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>1400</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>-700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-3100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>4700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-4700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>2900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KEWL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KEWL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="92">
   <si>
     <t>KEWL</t>
   </si>
@@ -656,119 +656,127 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>100</v>
+      <c r="D8" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E8" s="3">
         <v>100</v>
@@ -792,49 +800,55 @@
         <v>100</v>
       </c>
       <c r="L8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M8" s="3">
+        <v>100</v>
+      </c>
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
         <v>3500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>7700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>5400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>2300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>6100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>4700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>9500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>5500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>3500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>6200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -851,10 +865,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3">
         <v>100</v>
@@ -863,49 +877,55 @@
         <v>100</v>
       </c>
       <c r="L9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M9" s="3">
+        <v>100</v>
+      </c>
+      <c r="N9" s="3">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3">
         <v>2500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>4000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>3600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>3700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>1900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>4700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>3700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>8100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>1400</v>
-      </c>
-      <c r="V9" s="3">
-        <v>4000</v>
-      </c>
-      <c r="W9" s="3">
-        <v>3000</v>
       </c>
       <c r="X9" s="3">
         <v>4000</v>
       </c>
       <c r="Y9" s="3">
+        <v>3000</v>
+      </c>
+      <c r="Z9" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AA9" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -922,10 +942,10 @@
         <v>100</v>
       </c>
       <c r="H10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J10" s="3">
         <v>0</v>
@@ -937,46 +957,52 @@
         <v>0</v>
       </c>
       <c r="M10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3">
         <v>1000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>3700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>-3400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>400</v>
-      </c>
-      <c r="R10" s="3">
-        <v>1400</v>
-      </c>
-      <c r="S10" s="3">
-        <v>1000</v>
       </c>
       <c r="T10" s="3">
         <v>1400</v>
       </c>
       <c r="U10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V10" s="3">
+        <v>1400</v>
+      </c>
+      <c r="W10" s="3">
         <v>300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>1500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>2200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1002,8 +1028,10 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1073,8 +1101,14 @@
       <c r="Y12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,35 +1178,41 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>-200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>-200</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>-200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-200</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1182,11 +1222,11 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1195,28 +1235,34 @@
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>200</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1286,8 +1332,14 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,8 +1362,10 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1343,46 +1397,52 @@
         <v>200</v>
       </c>
       <c r="M17" s="3">
+        <v>200</v>
+      </c>
+      <c r="N17" s="3">
+        <v>200</v>
+      </c>
+      <c r="O17" s="3">
         <v>3100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>4600</v>
       </c>
-      <c r="O17" s="3">
-        <v>100</v>
-      </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
+        <v>100</v>
+      </c>
+      <c r="R17" s="3">
         <v>4100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>2300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>5200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>4100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>8700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>4900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>3400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>4800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1411,49 +1471,55 @@
         <v>-100</v>
       </c>
       <c r="L18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N18" s="3">
         <v>-200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>3100</v>
       </c>
-      <c r="O18" s="3">
-        <v>100</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
+        <v>100</v>
+      </c>
+      <c r="R18" s="3">
         <v>1300</v>
       </c>
-      <c r="Q18" s="3">
-        <v>0</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
+        <v>0</v>
+      </c>
+      <c r="T18" s="3">
         <v>900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>600</v>
       </c>
-      <c r="W18" s="3">
-        <v>100</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z18" s="3">
         <v>1400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,8 +1545,10 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1496,35 +1564,35 @@
       <c r="G20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
+      <c r="N20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
       <c r="Q20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -1539,19 +1607,25 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>1500</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1568,61 +1642,67 @@
         <v>-100</v>
       </c>
       <c r="H21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J21" s="3">
         <v>-300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-300</v>
       </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
       <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3">
         <v>-200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>3300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>1000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>1500</v>
       </c>
-      <c r="Q21" s="3">
-        <v>100</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
+        <v>100</v>
+      </c>
+      <c r="T21" s="3">
         <v>1100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>1000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>2400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>1600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1653,17 +1733,17 @@
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="3">
-        <v>100</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O22" s="3">
         <v>100</v>
       </c>
       <c r="P22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="3">
         <v>100</v>
@@ -1678,10 +1758,10 @@
         <v>100</v>
       </c>
       <c r="U22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W22" s="3">
         <v>200</v>
@@ -1692,23 +1772,29 @@
       <c r="Y22" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
         <v>200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>200</v>
       </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
       <c r="H23" s="3">
         <v>0</v>
       </c>
@@ -1716,55 +1802,61 @@
         <v>0</v>
       </c>
       <c r="J23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L23" s="3">
+        <v>100</v>
+      </c>
+      <c r="M23" s="3">
+        <v>100</v>
+      </c>
+      <c r="N23" s="3">
         <v>-200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>3100</v>
       </c>
-      <c r="O23" s="3">
-        <v>100</v>
-      </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
+        <v>100</v>
+      </c>
+      <c r="R23" s="3">
         <v>1200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>2000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>1200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1793,49 +1885,55 @@
         <v>0</v>
       </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
-        <v>100</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
+        <v>100</v>
+      </c>
+      <c r="P24" s="3">
         <v>800</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>300</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3">
-        <v>200</v>
-      </c>
       <c r="S24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T24" s="3">
         <v>200</v>
       </c>
       <c r="U24" s="3">
+        <v>100</v>
+      </c>
+      <c r="V24" s="3">
+        <v>200</v>
+      </c>
+      <c r="W24" s="3">
         <v>-100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-200</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,22 +2003,28 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H26" s="3">
         <v>0</v>
@@ -1929,69 +2033,75 @@
         <v>0</v>
       </c>
       <c r="J26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L26" s="3">
+        <v>100</v>
+      </c>
+      <c r="M26" s="3">
+        <v>100</v>
+      </c>
+      <c r="N26" s="3">
         <v>-200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>2300</v>
       </c>
-      <c r="O26" s="3">
-        <v>100</v>
-      </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
+        <v>100</v>
+      </c>
+      <c r="R26" s="3">
         <v>900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>1500</v>
       </c>
-      <c r="W26" s="3">
-        <v>100</v>
-      </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z26" s="3">
         <v>1200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H27" s="3">
         <v>0</v>
@@ -2000,55 +2110,61 @@
         <v>0</v>
       </c>
       <c r="J27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L27" s="3">
+        <v>100</v>
+      </c>
+      <c r="M27" s="3">
+        <v>100</v>
+      </c>
+      <c r="N27" s="3">
         <v>-200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>2300</v>
       </c>
-      <c r="O27" s="3">
-        <v>100</v>
-      </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
+        <v>100</v>
+      </c>
+      <c r="R27" s="3">
         <v>900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>1500</v>
       </c>
-      <c r="W27" s="3">
-        <v>100</v>
-      </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z27" s="3">
         <v>1200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2234,14 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2148,28 +2270,28 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-100</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O29" s="3">
+      <c r="O29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3">
         <v>3300</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
-      <c r="S29" s="3">
-        <v>0</v>
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T29" s="3">
         <v>0</v>
@@ -2189,8 +2311,14 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2388,14 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,8 +2465,14 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2348,36 +2488,36 @@
       <c r="G32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
-        <v>100</v>
-      </c>
-      <c r="K32" s="3">
-        <v>100</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>8</v>
+      <c r="L32" s="3">
+        <v>100</v>
       </c>
       <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -2391,33 +2531,39 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-1500</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H33" s="3">
         <v>0</v>
@@ -2426,55 +2572,61 @@
         <v>0</v>
       </c>
       <c r="J33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L33" s="3">
+        <v>100</v>
+      </c>
+      <c r="M33" s="3">
+        <v>100</v>
+      </c>
+      <c r="N33" s="3">
         <v>-200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>2300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>3400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>1500</v>
       </c>
-      <c r="W33" s="3">
-        <v>100</v>
-      </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z33" s="3">
         <v>1200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,22 +2696,28 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H35" s="3">
         <v>0</v>
@@ -2568,131 +2726,143 @@
         <v>0</v>
       </c>
       <c r="J35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L35" s="3">
+        <v>100</v>
+      </c>
+      <c r="M35" s="3">
+        <v>100</v>
+      </c>
+      <c r="N35" s="3">
         <v>-200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>2300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>3400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>1500</v>
       </c>
-      <c r="W35" s="3">
-        <v>100</v>
-      </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z35" s="3">
         <v>1200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2888,10 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,8 +2917,10 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2757,67 +2931,73 @@
         <v>4100</v>
       </c>
       <c r="F41" s="3">
+        <v>4100</v>
+      </c>
+      <c r="G41" s="3">
+        <v>4100</v>
+      </c>
+      <c r="H41" s="3">
         <v>4000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>4000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>8400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>8400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>10100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>10100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>9900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>2500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>3100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>1600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>2400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>5700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>5600</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2887,8 +3067,14 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2917,49 +3103,55 @@
         <v>100</v>
       </c>
       <c r="L43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M43" s="3">
+        <v>100</v>
+      </c>
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3">
         <v>1400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>2000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>900</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2990,47 +3182,53 @@
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O44" s="3">
         <v>200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>300</v>
       </c>
-      <c r="Q44" s="3">
-        <v>100</v>
-      </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
+        <v>100</v>
+      </c>
+      <c r="T44" s="3">
         <v>200</v>
       </c>
-      <c r="S44" s="3">
-        <v>100</v>
-      </c>
-      <c r="T44" s="3">
-        <v>100</v>
-      </c>
       <c r="U44" s="3">
         <v>100</v>
       </c>
       <c r="V44" s="3">
         <v>100</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X44" s="3" t="s">
-        <v>8</v>
+      <c r="W44" s="3">
+        <v>100</v>
+      </c>
+      <c r="X44" s="3">
+        <v>100</v>
       </c>
       <c r="Y44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3052,38 +3250,38 @@
       <c r="I45" s="3">
         <v>100</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>8</v>
+      <c r="J45" s="3">
+        <v>100</v>
+      </c>
+      <c r="K45" s="3">
+        <v>100</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O45" s="3">
         <v>2800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>2700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>300</v>
-      </c>
-      <c r="P45" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>600</v>
       </c>
       <c r="R45" s="3">
         <v>600</v>
       </c>
       <c r="S45" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="T45" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="U45" s="3">
         <v>400</v>
@@ -3091,88 +3289,100 @@
       <c r="V45" s="3">
         <v>400</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X45" s="3" t="s">
-        <v>8</v>
+      <c r="W45" s="3">
+        <v>400</v>
+      </c>
+      <c r="X45" s="3">
+        <v>400</v>
       </c>
       <c r="Y45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F46" s="3">
         <v>4400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>4400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>4200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>4200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>8600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>8600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>10200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>10200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>10000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>6100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>7000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>4200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>4900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>3400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>3800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>4100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>7600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>2200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>7000</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3188,11 +3398,11 @@
       <c r="G47" s="3">
         <v>2000</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>8</v>
+      <c r="H47" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I47" s="3">
+        <v>2000</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>8</v>
@@ -3203,11 +3413,11 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -3242,79 +3452,91 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>8400</v>
+      </c>
+      <c r="F48" s="3">
         <v>8300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>8300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>8100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>8100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>7100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>7100</v>
-      </c>
-      <c r="J48" s="3">
-        <v>5600</v>
-      </c>
-      <c r="K48" s="3">
-        <v>5600</v>
       </c>
       <c r="L48" s="3">
         <v>5600</v>
       </c>
       <c r="M48" s="3">
+        <v>5600</v>
+      </c>
+      <c r="N48" s="3">
+        <v>5600</v>
+      </c>
+      <c r="O48" s="3">
         <v>27200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>27200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>27700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>27700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>27900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>28000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>28200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>28300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>32800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>32800</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3384,8 +3606,14 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3683,14 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,8 +3760,14 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3558,20 +3798,20 @@
       <c r="L52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M52" s="3">
-        <v>100</v>
-      </c>
-      <c r="N52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O52" s="3">
+        <v>100</v>
+      </c>
+      <c r="P52" s="3">
         <v>200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>200</v>
-      </c>
-      <c r="P52" s="3">
-        <v>400</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>400</v>
       </c>
       <c r="R52" s="3">
         <v>400</v>
@@ -3588,17 +3828,23 @@
       <c r="V52" s="3">
         <v>400</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X52" s="3" t="s">
-        <v>8</v>
+      <c r="W52" s="3">
+        <v>400</v>
+      </c>
+      <c r="X52" s="3">
+        <v>400</v>
       </c>
       <c r="Y52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,8 +3914,14 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -3680,16 +3932,16 @@
         <v>14700</v>
       </c>
       <c r="F54" s="3">
+        <v>14700</v>
+      </c>
+      <c r="G54" s="3">
+        <v>14700</v>
+      </c>
+      <c r="H54" s="3">
         <v>14300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>14300</v>
-      </c>
-      <c r="H54" s="3">
-        <v>15700</v>
-      </c>
-      <c r="I54" s="3">
-        <v>15700</v>
       </c>
       <c r="J54" s="3">
         <v>15700</v>
@@ -3698,49 +3950,55 @@
         <v>15700</v>
       </c>
       <c r="L54" s="3">
+        <v>15700</v>
+      </c>
+      <c r="M54" s="3">
+        <v>15700</v>
+      </c>
+      <c r="N54" s="3">
         <v>15600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>33400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>34300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>32100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>33000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>31700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>32200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>32700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>36200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>35300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>40200</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +4024,10 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,8 +4053,10 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3826,46 +4088,52 @@
         <v>0</v>
       </c>
       <c r="M57" s="3">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3">
+        <v>0</v>
+      </c>
+      <c r="O57" s="3">
         <v>300</v>
       </c>
-      <c r="N57" s="3">
-        <v>100</v>
-      </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q57" s="3">
         <v>200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>400</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>300</v>
-      </c>
-      <c r="R57" s="3">
-        <v>200</v>
       </c>
       <c r="S57" s="3">
         <v>300</v>
       </c>
       <c r="T57" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="U57" s="3">
         <v>300</v>
       </c>
       <c r="V57" s="3">
+        <v>400</v>
+      </c>
+      <c r="W57" s="3">
+        <v>300</v>
+      </c>
+      <c r="X57" s="3">
         <v>200</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3897,25 +4165,25 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>1500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>2500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>2500</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>8</v>
@@ -3923,8 +4191,8 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
+      <c r="V58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -3935,8 +4203,14 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3946,11 +4220,11 @@
       <c r="E59" s="3">
         <v>0</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>8</v>
+      <c r="F59" s="3">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3">
+        <v>0</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>8</v>
@@ -3967,47 +4241,53 @@
       <c r="L59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O59" s="3">
         <v>500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>500</v>
-      </c>
-      <c r="R59" s="3">
-        <v>500</v>
-      </c>
-      <c r="S59" s="3">
-        <v>700</v>
       </c>
       <c r="T59" s="3">
         <v>500</v>
       </c>
       <c r="U59" s="3">
+        <v>700</v>
+      </c>
+      <c r="V59" s="3">
         <v>500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
+        <v>500</v>
+      </c>
+      <c r="X59" s="3">
         <v>1100</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4030,55 +4310,61 @@
         <v>0</v>
       </c>
       <c r="J60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L60" s="3">
         <v>100</v>
       </c>
       <c r="M60" s="3">
+        <v>100</v>
+      </c>
+      <c r="N60" s="3">
+        <v>100</v>
+      </c>
+      <c r="O60" s="3">
         <v>2300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>3600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>3800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1300</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4110,46 +4396,52 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>3500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>3500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>4000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>9600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>9500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>9500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>10000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>14000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>14000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>18000</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4180,21 +4472,21 @@
       <c r="L62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O62" s="3">
         <v>700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>200</v>
       </c>
-      <c r="P62" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>100</v>
-      </c>
       <c r="R62" s="3">
         <v>100</v>
       </c>
@@ -4208,19 +4500,25 @@
         <v>100</v>
       </c>
       <c r="V62" s="3">
+        <v>100</v>
+      </c>
+      <c r="W62" s="3">
+        <v>100</v>
+      </c>
+      <c r="X62" s="3">
         <v>200</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4588,14 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4665,14 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,8 +4742,14 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -4444,10 +4760,10 @@
         <v>400</v>
       </c>
       <c r="F66" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G66" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H66" s="3">
         <v>300</v>
@@ -4465,46 +4781,52 @@
         <v>300</v>
       </c>
       <c r="M66" s="3">
+        <v>300</v>
+      </c>
+      <c r="N66" s="3">
+        <v>300</v>
+      </c>
+      <c r="O66" s="3">
         <v>6500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>7700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>7900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>10800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>10500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>10400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>11100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>15000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>14900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>19500</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4852,10 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4925,14 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +5002,14 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4743,8 +5079,14 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,8 +5156,14 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -4826,16 +5174,16 @@
         <v>14100</v>
       </c>
       <c r="F72" s="3">
+        <v>14100</v>
+      </c>
+      <c r="G72" s="3">
+        <v>14100</v>
+      </c>
+      <c r="H72" s="3">
         <v>13900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>13900</v>
-      </c>
-      <c r="H72" s="3">
-        <v>15300</v>
-      </c>
-      <c r="I72" s="3">
-        <v>15300</v>
       </c>
       <c r="J72" s="3">
         <v>15300</v>
@@ -4844,49 +5192,55 @@
         <v>15300</v>
       </c>
       <c r="L72" s="3">
+        <v>15300</v>
+      </c>
+      <c r="M72" s="3">
+        <v>15300</v>
+      </c>
+      <c r="N72" s="3">
         <v>15200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>26900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>26500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>24200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>22200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>21100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>21700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>21500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>21100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>20400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>20600</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5310,14 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5387,14 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,8 +5464,14 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -5110,16 +5482,16 @@
         <v>14300</v>
       </c>
       <c r="F76" s="3">
+        <v>14300</v>
+      </c>
+      <c r="G76" s="3">
+        <v>14300</v>
+      </c>
+      <c r="H76" s="3">
         <v>14000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>14000</v>
-      </c>
-      <c r="H76" s="3">
-        <v>15400</v>
-      </c>
-      <c r="I76" s="3">
-        <v>15400</v>
       </c>
       <c r="J76" s="3">
         <v>15400</v>
@@ -5128,49 +5500,55 @@
         <v>15400</v>
       </c>
       <c r="L76" s="3">
+        <v>15400</v>
+      </c>
+      <c r="M76" s="3">
+        <v>15400</v>
+      </c>
+      <c r="N76" s="3">
         <v>15200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>26900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>26500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>24300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>22200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>21200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>21800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>21600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>21200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>20500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>20700</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,98 +5618,110 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H81" s="3">
         <v>0</v>
@@ -5340,55 +5730,61 @@
         <v>0</v>
       </c>
       <c r="J81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L81" s="3">
+        <v>100</v>
+      </c>
+      <c r="M81" s="3">
+        <v>100</v>
+      </c>
+      <c r="N81" s="3">
         <v>-200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>2300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>3400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>1500</v>
       </c>
-      <c r="W81" s="3">
-        <v>100</v>
-      </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z81" s="3">
         <v>1200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,8 +5810,10 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5443,50 +5841,56 @@
       <c r="K83" s="3">
         <v>0</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>8</v>
+      <c r="L83" s="3">
+        <v>0</v>
       </c>
       <c r="M83" s="3">
-        <v>100</v>
-      </c>
-      <c r="N83" s="3">
-        <v>200</v>
+        <v>0</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O83" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="P83" s="3">
         <v>200</v>
       </c>
       <c r="Q83" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="R83" s="3">
         <v>200</v>
       </c>
       <c r="S83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T83" s="3">
         <v>200</v>
       </c>
       <c r="U83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V83" s="3">
         <v>200</v>
       </c>
       <c r="W83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X83" s="3">
         <v>200</v>
       </c>
       <c r="Y83" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5960,14 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +6037,14 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +6114,14 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +6191,14 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,22 +6268,28 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H89" s="3">
         <v>0</v>
@@ -5870,49 +6304,55 @@
         <v>0</v>
       </c>
       <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3">
         <v>-200</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3">
         <v>1400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>1800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>1000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>300</v>
       </c>
-      <c r="R89" s="3">
-        <v>100</v>
-      </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
+        <v>100</v>
+      </c>
+      <c r="U89" s="3">
         <v>1200</v>
       </c>
-      <c r="T89" s="3">
-        <v>100</v>
-      </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
+        <v>100</v>
+      </c>
+      <c r="W89" s="3">
         <v>-700</v>
       </c>
-      <c r="V89" s="3">
-        <v>100</v>
-      </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,8 +6378,10 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5950,23 +6392,23 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-800</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
@@ -5974,14 +6416,14 @@
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
@@ -6001,16 +6443,22 @@
         <v>0</v>
       </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6528,14 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,8 +6605,14 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6163,67 +6623,73 @@
         <v>0</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-1500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-1500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-800</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>2700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>1600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>200</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3">
-        <v>100</v>
-      </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
+        <v>100</v>
+      </c>
+      <c r="V94" s="3">
         <v>4400</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>3200</v>
-      </c>
-      <c r="W94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="X94" s="3">
-        <v>1200</v>
       </c>
       <c r="Y94" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AA94" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,8 +6715,10 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6281,11 +6749,11 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -6320,8 +6788,14 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6865,14 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6942,14 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,79 +7019,91 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-700</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N100" s="3">
         <v>-2300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-1000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-4600</v>
       </c>
-      <c r="P100" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
+        <v>100</v>
+      </c>
+      <c r="S100" s="3">
         <v>-500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-4100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-4000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-400</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6636,11 +7134,11 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -6675,75 +7173,87 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F102" s="3">
+        <v>100</v>
+      </c>
+      <c r="G102" s="3">
+        <v>100</v>
+      </c>
+      <c r="H102" s="3">
         <v>-2200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-2200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-800</v>
       </c>
-      <c r="J102" s="3">
-        <v>100</v>
-      </c>
-      <c r="K102" s="3">
-        <v>100</v>
-      </c>
       <c r="L102" s="3">
+        <v>100</v>
+      </c>
+      <c r="M102" s="3">
+        <v>100</v>
+      </c>
+      <c r="N102" s="3">
         <v>-2600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>3600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-1100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>1400</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>-700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-3100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>4700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-4700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>2900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KEWL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KEWL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="92">
   <si>
     <t>KEWL</t>
   </si>
@@ -656,127 +656,134 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>8</v>
+      <c r="D8" s="3">
+        <v>100</v>
       </c>
       <c r="E8" s="3">
         <v>100</v>
@@ -806,57 +813,63 @@
         <v>100</v>
       </c>
       <c r="N8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O8" s="3">
+        <v>100</v>
+      </c>
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
         <v>3500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>7700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>5400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>2300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>6100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>4700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>9500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>5500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>3500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>6200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9" s="3">
         <v>0</v>
@@ -871,10 +884,10 @@
         <v>0</v>
       </c>
       <c r="J9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L9" s="3">
         <v>100</v>
@@ -883,49 +896,55 @@
         <v>100</v>
       </c>
       <c r="N9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O9" s="3">
+        <v>100</v>
+      </c>
+      <c r="P9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3">
         <v>2500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>4000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>3600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>3700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>1900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>4700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>3700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>8100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>1400</v>
-      </c>
-      <c r="X9" s="3">
-        <v>4000</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>3000</v>
       </c>
       <c r="Z9" s="3">
         <v>4000</v>
       </c>
       <c r="AA9" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AB9" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AC9" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -948,10 +967,10 @@
         <v>100</v>
       </c>
       <c r="J10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10" s="3">
         <v>0</v>
@@ -963,46 +982,52 @@
         <v>0</v>
       </c>
       <c r="O10" s="3">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3">
         <v>1000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>3700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>-3400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>400</v>
-      </c>
-      <c r="T10" s="3">
-        <v>1400</v>
-      </c>
-      <c r="U10" s="3">
-        <v>1000</v>
       </c>
       <c r="V10" s="3">
         <v>1400</v>
       </c>
       <c r="W10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="X10" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Y10" s="3">
         <v>300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>1500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>2200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1030,8 +1055,10 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1107,8 +1134,14 @@
       <c r="AA12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1184,8 +1217,14 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1196,29 +1235,29 @@
         <v>0</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>-200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>-200</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>-200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-200</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1228,11 +1267,11 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1241,28 +1280,34 @@
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>200</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>300</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1338,8 +1383,14 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1364,8 +1415,10 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1403,46 +1456,52 @@
         <v>200</v>
       </c>
       <c r="O17" s="3">
+        <v>200</v>
+      </c>
+      <c r="P17" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q17" s="3">
         <v>3100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>4600</v>
       </c>
-      <c r="Q17" s="3">
-        <v>100</v>
-      </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
+        <v>100</v>
+      </c>
+      <c r="T17" s="3">
         <v>4100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>2300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>5200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>4100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>8700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>4900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>3400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>4800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1477,49 +1536,55 @@
         <v>-100</v>
       </c>
       <c r="N18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P18" s="3">
         <v>-200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>3100</v>
       </c>
-      <c r="Q18" s="3">
-        <v>100</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
+        <v>100</v>
+      </c>
+      <c r="T18" s="3">
         <v>1300</v>
       </c>
-      <c r="S18" s="3">
-        <v>0</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3">
         <v>900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>600</v>
       </c>
-      <c r="Y18" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB18" s="3">
         <v>1400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1547,8 +1612,10 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1570,35 +1637,35 @@
       <c r="I20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
+      <c r="P20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
       <c r="S20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T20" s="3">
         <v>0</v>
@@ -1613,19 +1680,25 @@
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>1500</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1648,61 +1721,67 @@
         <v>-100</v>
       </c>
       <c r="J21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L21" s="3">
         <v>-300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-300</v>
       </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
       <c r="N21" s="3">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3">
         <v>-200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>3300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>1000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>1500</v>
       </c>
-      <c r="S21" s="3">
-        <v>100</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
+        <v>100</v>
+      </c>
+      <c r="V21" s="3">
         <v>1100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>1000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>2400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>1600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1739,17 +1818,17 @@
       <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O22" s="3">
-        <v>100</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q22" s="3">
         <v>100</v>
       </c>
       <c r="R22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S22" s="3">
         <v>100</v>
@@ -1764,10 +1843,10 @@
         <v>100</v>
       </c>
       <c r="W22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y22" s="3">
         <v>200</v>
@@ -1778,8 +1857,14 @@
       <c r="AA22" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1790,17 +1875,17 @@
         <v>0</v>
       </c>
       <c r="F23" s="3">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
         <v>200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>200</v>
       </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
-      <c r="I23" s="3">
-        <v>0</v>
-      </c>
       <c r="J23" s="3">
         <v>0</v>
       </c>
@@ -1808,55 +1893,61 @@
         <v>0</v>
       </c>
       <c r="L23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N23" s="3">
+        <v>100</v>
+      </c>
+      <c r="O23" s="3">
+        <v>100</v>
+      </c>
+      <c r="P23" s="3">
         <v>-200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>3100</v>
       </c>
-      <c r="Q23" s="3">
-        <v>100</v>
-      </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
+        <v>100</v>
+      </c>
+      <c r="T23" s="3">
         <v>1200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>2000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>1200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1891,49 +1982,55 @@
         <v>0</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="O24" s="3">
-        <v>100</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
+        <v>100</v>
+      </c>
+      <c r="R24" s="3">
         <v>800</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>300</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
-      <c r="T24" s="3">
-        <v>200</v>
-      </c>
       <c r="U24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V24" s="3">
         <v>200</v>
       </c>
       <c r="W24" s="3">
+        <v>100</v>
+      </c>
+      <c r="X24" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y24" s="3">
         <v>-100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-200</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2009,8 +2106,14 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2021,16 +2124,16 @@
         <v>0</v>
       </c>
       <c r="F26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J26" s="3">
         <v>0</v>
@@ -2039,55 +2142,61 @@
         <v>0</v>
       </c>
       <c r="L26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N26" s="3">
+        <v>100</v>
+      </c>
+      <c r="O26" s="3">
+        <v>100</v>
+      </c>
+      <c r="P26" s="3">
         <v>-200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>2300</v>
       </c>
-      <c r="Q26" s="3">
-        <v>100</v>
-      </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
+        <v>100</v>
+      </c>
+      <c r="T26" s="3">
         <v>900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>1500</v>
       </c>
-      <c r="Y26" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB26" s="3">
         <v>1200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2098,16 +2207,16 @@
         <v>0</v>
       </c>
       <c r="F27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J27" s="3">
         <v>0</v>
@@ -2116,55 +2225,61 @@
         <v>0</v>
       </c>
       <c r="L27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N27" s="3">
+        <v>100</v>
+      </c>
+      <c r="O27" s="3">
+        <v>100</v>
+      </c>
+      <c r="P27" s="3">
         <v>-200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>2300</v>
       </c>
-      <c r="Q27" s="3">
-        <v>100</v>
-      </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
+        <v>100</v>
+      </c>
+      <c r="T27" s="3">
         <v>900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>1500</v>
       </c>
-      <c r="Y27" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB27" s="3">
         <v>1200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2240,8 +2355,14 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2276,28 +2397,28 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>-100</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q29" s="3">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3">
         <v>3300</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="T29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
@@ -2317,8 +2438,14 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2394,8 +2521,14 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2471,8 +2604,14 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2494,36 +2633,36 @@
       <c r="I32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
-        <v>100</v>
-      </c>
-      <c r="M32" s="3">
-        <v>100</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>8</v>
+      <c r="N32" s="3">
+        <v>100</v>
       </c>
       <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -2537,19 +2676,25 @@
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2560,16 +2705,16 @@
         <v>0</v>
       </c>
       <c r="F33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J33" s="3">
         <v>0</v>
@@ -2578,55 +2723,61 @@
         <v>0</v>
       </c>
       <c r="L33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N33" s="3">
+        <v>100</v>
+      </c>
+      <c r="O33" s="3">
+        <v>100</v>
+      </c>
+      <c r="P33" s="3">
         <v>-200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>2300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>3400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>1500</v>
       </c>
-      <c r="Y33" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB33" s="3">
         <v>1200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2702,8 +2853,14 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2714,16 +2871,16 @@
         <v>0</v>
       </c>
       <c r="F35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J35" s="3">
         <v>0</v>
@@ -2732,137 +2889,149 @@
         <v>0</v>
       </c>
       <c r="L35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N35" s="3">
+        <v>100</v>
+      </c>
+      <c r="O35" s="3">
+        <v>100</v>
+      </c>
+      <c r="P35" s="3">
         <v>-200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>2300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>3400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>1500</v>
       </c>
-      <c r="Y35" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB35" s="3">
         <v>1200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2890,8 +3059,10 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2919,16 +3090,18 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>4100</v>
+        <v>4200</v>
       </c>
       <c r="E41" s="3">
-        <v>4100</v>
+        <v>4200</v>
       </c>
       <c r="F41" s="3">
         <v>4100</v>
@@ -2937,67 +3110,73 @@
         <v>4100</v>
       </c>
       <c r="H41" s="3">
+        <v>4100</v>
+      </c>
+      <c r="I41" s="3">
+        <v>4100</v>
+      </c>
+      <c r="J41" s="3">
         <v>4000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>4000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>8400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>8400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>10100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>10100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>9900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>2500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>3100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>2400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>5700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>5600</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3073,16 +3252,22 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F43" s="3">
         <v>100</v>
@@ -3091,10 +3276,10 @@
         <v>100</v>
       </c>
       <c r="H43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J43" s="3">
         <v>100</v>
@@ -3109,49 +3294,55 @@
         <v>100</v>
       </c>
       <c r="N43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O43" s="3">
+        <v>100</v>
+      </c>
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
         <v>1400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>2000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>1100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>1400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>900</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3188,55 +3379,61 @@
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O44" s="3">
+      <c r="O44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q44" s="3">
         <v>200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>300</v>
       </c>
-      <c r="S44" s="3">
-        <v>100</v>
-      </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
+        <v>100</v>
+      </c>
+      <c r="V44" s="3">
         <v>200</v>
       </c>
-      <c r="U44" s="3">
-        <v>100</v>
-      </c>
-      <c r="V44" s="3">
-        <v>100</v>
-      </c>
       <c r="W44" s="3">
         <v>100</v>
       </c>
       <c r="X44" s="3">
         <v>100</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z44" s="3" t="s">
-        <v>8</v>
+      <c r="Y44" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z44" s="3">
+        <v>100</v>
       </c>
       <c r="AA44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>100</v>
-      </c>
-      <c r="E45" s="3">
-        <v>100</v>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F45" s="3">
         <v>100</v>
@@ -3244,11 +3441,11 @@
       <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="H45" s="3">
-        <v>100</v>
-      </c>
-      <c r="I45" s="3">
-        <v>100</v>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J45" s="3">
         <v>100</v>
@@ -3256,38 +3453,38 @@
       <c r="K45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>8</v>
+      <c r="L45" s="3">
+        <v>100</v>
+      </c>
+      <c r="M45" s="3">
+        <v>100</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3">
         <v>2800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>2700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>300</v>
-      </c>
-      <c r="R45" s="3">
-        <v>600</v>
-      </c>
-      <c r="S45" s="3">
-        <v>600</v>
       </c>
       <c r="T45" s="3">
         <v>600</v>
       </c>
       <c r="U45" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="V45" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="W45" s="3">
         <v>400</v>
@@ -3295,17 +3492,23 @@
       <c r="X45" s="3">
         <v>400</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z45" s="3" t="s">
-        <v>8</v>
+      <c r="Y45" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z45" s="3">
+        <v>400</v>
       </c>
       <c r="AA45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3316,73 +3519,79 @@
         <v>4300</v>
       </c>
       <c r="F46" s="3">
+        <v>4300</v>
+      </c>
+      <c r="G46" s="3">
+        <v>4300</v>
+      </c>
+      <c r="H46" s="3">
         <v>4400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>4400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>4200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>4200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>8600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>8600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>10200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>10200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>10000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>6100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>7000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>4200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>4900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>3400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>3800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>4100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>7600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>2200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>7000</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3404,11 +3613,11 @@
       <c r="I47" s="3">
         <v>2000</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>8</v>
+      <c r="J47" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K47" s="3">
+        <v>2000</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>8</v>
@@ -3419,11 +3628,11 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3458,8 +3667,14 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3470,73 +3685,79 @@
         <v>8400</v>
       </c>
       <c r="F48" s="3">
+        <v>8400</v>
+      </c>
+      <c r="G48" s="3">
+        <v>8400</v>
+      </c>
+      <c r="H48" s="3">
         <v>8300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>8300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>8100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>8100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>7100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>7100</v>
-      </c>
-      <c r="L48" s="3">
-        <v>5600</v>
-      </c>
-      <c r="M48" s="3">
-        <v>5600</v>
       </c>
       <c r="N48" s="3">
         <v>5600</v>
       </c>
       <c r="O48" s="3">
+        <v>5600</v>
+      </c>
+      <c r="P48" s="3">
+        <v>5600</v>
+      </c>
+      <c r="Q48" s="3">
         <v>27200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>27200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>27700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>27700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>27900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>28000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>28200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>28300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>32800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>32800</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3612,8 +3833,14 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3689,8 +3916,14 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3766,8 +3999,14 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3804,20 +4043,20 @@
       <c r="N52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O52" s="3">
-        <v>100</v>
-      </c>
-      <c r="P52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>100</v>
+      </c>
+      <c r="R52" s="3">
         <v>200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>200</v>
-      </c>
-      <c r="R52" s="3">
-        <v>400</v>
-      </c>
-      <c r="S52" s="3">
-        <v>400</v>
       </c>
       <c r="T52" s="3">
         <v>400</v>
@@ -3834,17 +4073,23 @@
       <c r="X52" s="3">
         <v>400</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z52" s="3" t="s">
-        <v>8</v>
+      <c r="Y52" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z52" s="3">
+        <v>400</v>
       </c>
       <c r="AA52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3920,8 +4165,14 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -3938,16 +4189,16 @@
         <v>14700</v>
       </c>
       <c r="H54" s="3">
+        <v>14700</v>
+      </c>
+      <c r="I54" s="3">
+        <v>14700</v>
+      </c>
+      <c r="J54" s="3">
         <v>14300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>14300</v>
-      </c>
-      <c r="J54" s="3">
-        <v>15700</v>
-      </c>
-      <c r="K54" s="3">
-        <v>15700</v>
       </c>
       <c r="L54" s="3">
         <v>15700</v>
@@ -3956,49 +4207,55 @@
         <v>15700</v>
       </c>
       <c r="N54" s="3">
+        <v>15700</v>
+      </c>
+      <c r="O54" s="3">
+        <v>15700</v>
+      </c>
+      <c r="P54" s="3">
         <v>15600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>33400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>34300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>32100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>33000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>31700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>32200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>32700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>36200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>35300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>40200</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4026,8 +4283,10 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4055,8 +4314,10 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4094,46 +4355,52 @@
         <v>0</v>
       </c>
       <c r="O57" s="3">
+        <v>0</v>
+      </c>
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3">
         <v>300</v>
       </c>
-      <c r="P57" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
+        <v>100</v>
+      </c>
+      <c r="S57" s="3">
         <v>200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>400</v>
-      </c>
-      <c r="S57" s="3">
-        <v>300</v>
-      </c>
-      <c r="T57" s="3">
-        <v>200</v>
       </c>
       <c r="U57" s="3">
         <v>300</v>
       </c>
       <c r="V57" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="W57" s="3">
         <v>300</v>
       </c>
       <c r="X57" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y57" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z57" s="3">
         <v>200</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4171,25 +4438,25 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>1500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>2500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>2500</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>8</v>
@@ -4197,8 +4464,8 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
+      <c r="X58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y58" s="3">
         <v>0</v>
@@ -4209,16 +4476,22 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
-      </c>
-      <c r="E59" s="3">
-        <v>0</v>
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F59" s="3">
         <v>0</v>
@@ -4226,11 +4499,11 @@
       <c r="G59" s="3">
         <v>0</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>8</v>
+      <c r="H59" s="3">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
+        <v>0</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>8</v>
@@ -4247,47 +4520,53 @@
       <c r="N59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q59" s="3">
         <v>500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>500</v>
-      </c>
-      <c r="T59" s="3">
-        <v>500</v>
-      </c>
-      <c r="U59" s="3">
-        <v>700</v>
       </c>
       <c r="V59" s="3">
         <v>500</v>
       </c>
       <c r="W59" s="3">
+        <v>700</v>
+      </c>
+      <c r="X59" s="3">
         <v>500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z59" s="3">
         <v>1100</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4316,55 +4595,61 @@
         <v>0</v>
       </c>
       <c r="L60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N60" s="3">
         <v>100</v>
       </c>
       <c r="O60" s="3">
+        <v>100</v>
+      </c>
+      <c r="P60" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q60" s="3">
         <v>2300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>3600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>3800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>1300</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4402,46 +4687,52 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>3500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>3500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>4000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>9600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>9500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>9500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>10000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>14000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>14000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>18000</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4478,21 +4769,21 @@
       <c r="N62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q62" s="3">
         <v>700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>200</v>
       </c>
-      <c r="R62" s="3">
-        <v>100</v>
-      </c>
-      <c r="S62" s="3">
-        <v>100</v>
-      </c>
       <c r="T62" s="3">
         <v>100</v>
       </c>
@@ -4506,19 +4797,25 @@
         <v>100</v>
       </c>
       <c r="X62" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y62" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z62" s="3">
         <v>200</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4594,8 +4891,14 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4671,8 +4974,14 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4748,16 +5057,22 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E66" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F66" s="3">
         <v>400</v>
@@ -4766,10 +5081,10 @@
         <v>400</v>
       </c>
       <c r="H66" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="I66" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="J66" s="3">
         <v>300</v>
@@ -4787,46 +5102,52 @@
         <v>300</v>
       </c>
       <c r="O66" s="3">
+        <v>300</v>
+      </c>
+      <c r="P66" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q66" s="3">
         <v>6500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>7700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>7900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>10800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>10500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>10400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>11100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>15000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>14900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>19500</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4854,8 +5175,10 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4931,8 +5254,14 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5008,8 +5337,14 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5085,8 +5420,14 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5162,8 +5503,14 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -5180,16 +5527,16 @@
         <v>14100</v>
       </c>
       <c r="H72" s="3">
+        <v>14100</v>
+      </c>
+      <c r="I72" s="3">
+        <v>14100</v>
+      </c>
+      <c r="J72" s="3">
         <v>13900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>13900</v>
-      </c>
-      <c r="J72" s="3">
-        <v>15300</v>
-      </c>
-      <c r="K72" s="3">
-        <v>15300</v>
       </c>
       <c r="L72" s="3">
         <v>15300</v>
@@ -5198,49 +5545,55 @@
         <v>15300</v>
       </c>
       <c r="N72" s="3">
+        <v>15300</v>
+      </c>
+      <c r="O72" s="3">
+        <v>15300</v>
+      </c>
+      <c r="P72" s="3">
         <v>15200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>26900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>26500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>24200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>22200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>21100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>21700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>21500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>21100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>20400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>20600</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5316,8 +5669,14 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5393,8 +5752,14 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5470,8 +5835,14 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -5488,16 +5859,16 @@
         <v>14300</v>
       </c>
       <c r="H76" s="3">
+        <v>14300</v>
+      </c>
+      <c r="I76" s="3">
+        <v>14300</v>
+      </c>
+      <c r="J76" s="3">
         <v>14000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>14000</v>
-      </c>
-      <c r="J76" s="3">
-        <v>15400</v>
-      </c>
-      <c r="K76" s="3">
-        <v>15400</v>
       </c>
       <c r="L76" s="3">
         <v>15400</v>
@@ -5506,49 +5877,55 @@
         <v>15400</v>
       </c>
       <c r="N76" s="3">
+        <v>15400</v>
+      </c>
+      <c r="O76" s="3">
+        <v>15400</v>
+      </c>
+      <c r="P76" s="3">
         <v>15200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>26900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>26500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>24300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>22200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>21200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>21800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>21600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>21200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>20500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>20700</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5624,90 +6001,102 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5718,16 +6107,16 @@
         <v>0</v>
       </c>
       <c r="F81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J81" s="3">
         <v>0</v>
@@ -5736,55 +6125,61 @@
         <v>0</v>
       </c>
       <c r="L81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N81" s="3">
+        <v>100</v>
+      </c>
+      <c r="O81" s="3">
+        <v>100</v>
+      </c>
+      <c r="P81" s="3">
         <v>-200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>2300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>3400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>1500</v>
       </c>
-      <c r="Y81" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB81" s="3">
         <v>1200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5812,8 +6207,10 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5847,50 +6244,56 @@
       <c r="M83" s="3">
         <v>0</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>8</v>
+      <c r="N83" s="3">
+        <v>0</v>
       </c>
       <c r="O83" s="3">
-        <v>100</v>
-      </c>
-      <c r="P83" s="3">
-        <v>200</v>
+        <v>0</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q83" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="R83" s="3">
         <v>200</v>
       </c>
       <c r="S83" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="T83" s="3">
         <v>200</v>
       </c>
       <c r="U83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V83" s="3">
         <v>200</v>
       </c>
       <c r="W83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X83" s="3">
         <v>200</v>
       </c>
       <c r="Y83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z83" s="3">
         <v>200</v>
       </c>
       <c r="AA83" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AB83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5966,8 +6369,14 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6043,8 +6452,14 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6120,8 +6535,14 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6197,8 +6618,14 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6274,28 +6701,34 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J89" s="3">
         <v>0</v>
@@ -6310,49 +6743,55 @@
         <v>0</v>
       </c>
       <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3">
         <v>-200</v>
       </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+      <c r="R89" s="3">
         <v>1400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>1800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>1000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>300</v>
       </c>
-      <c r="T89" s="3">
-        <v>100</v>
-      </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
+        <v>100</v>
+      </c>
+      <c r="W89" s="3">
         <v>1200</v>
       </c>
-      <c r="V89" s="3">
-        <v>100</v>
-      </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-700</v>
       </c>
-      <c r="X89" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6380,8 +6819,10 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6398,23 +6839,23 @@
         <v>0</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-800</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
@@ -6422,14 +6863,14 @@
         <v>0</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
@@ -6449,16 +6890,22 @@
         <v>0</v>
       </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA91" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6534,8 +6981,14 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6611,8 +7064,14 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6629,67 +7088,73 @@
         <v>0</v>
       </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-1500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-800</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>2700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>1600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>200</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3">
-        <v>100</v>
-      </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
+        <v>100</v>
+      </c>
+      <c r="X94" s="3">
         <v>4400</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>3200</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Z94" s="3">
-        <v>1200</v>
       </c>
       <c r="AA94" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AC94" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6717,8 +7182,10 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6755,11 +7222,11 @@
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -6794,8 +7261,14 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6871,8 +7344,14 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6948,8 +7427,14 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7025,8 +7510,14 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7036,74 +7527,80 @@
       <c r="E100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
+      <c r="F100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-700</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P100" s="3">
         <v>-2300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-1000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-4600</v>
       </c>
-      <c r="R100" s="3">
-        <v>100</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
+        <v>100</v>
+      </c>
+      <c r="U100" s="3">
         <v>-500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-4100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-4000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-400</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7140,11 +7637,11 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -7179,81 +7676,93 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
+        <v>100</v>
+      </c>
+      <c r="I102" s="3">
+        <v>100</v>
+      </c>
+      <c r="J102" s="3">
         <v>-2200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-2200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-800</v>
       </c>
-      <c r="L102" s="3">
-        <v>100</v>
-      </c>
-      <c r="M102" s="3">
-        <v>100</v>
-      </c>
       <c r="N102" s="3">
+        <v>100</v>
+      </c>
+      <c r="O102" s="3">
+        <v>100</v>
+      </c>
+      <c r="P102" s="3">
         <v>-2600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>3600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>1400</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
         <v>-700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-3100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>4700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-4700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>2900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-500</v>
       </c>
     </row>
